--- a/010-npm_node/Testing_Book.xlsx
+++ b/010-npm_node/Testing_Book.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camdenbailey/Desktop/practice_notes/010-npm_node/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E688D0-481D-484C-896E-50C77D1AB04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB9CBFF-C7B1-8349-AAF3-9A52AB797DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="136">
   <si>
     <t>0</t>
   </si>
@@ -40,6 +40,9 @@
     <t>5</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>SECTION_ID</t>
   </si>
   <si>
@@ -64,259 +67,346 @@
     <t>A.</t>
   </si>
   <si>
-    <t>SINGLE FACE MONUMENT SIGN - ILLUMINATED W/ CHANNEL- LETTERS &amp; PUSH-THRU ACRYLIC. LOCATED @ MAIN ENTRY ON- FRONTAGE ROAD- *STRUCTURE AND POWER TO LOCATION BY OTHERS*</t>
+    <t>ILLUMINATED BLADE SIGN LOADS ON NW CORNER OF ADDISON- ROAD ELEVATION. CHANNEL LETTERS &amp; PUSH-THRU ACRYLIC COPY.- *BLOCKING AND POWER TO LOCATION BY OTHERS*</t>
   </si>
   <si>
     <t>B.</t>
   </si>
   <si>
-    <t>SINGLE FACE MONOLITH DIRECTIONAL SIGN</t>
+    <t>ILLUMINATED PARKING BUTTON / PROJECTING SIGN AT GARAGE- ENTRY OFF AIRPORT PARKWAY.- *BLOCKING AND POWER TO LOCATION BY OTHERS*</t>
   </si>
   <si>
     <t>C.</t>
   </si>
   <si>
-    <t>ILLUMINATED WALL SIGN - LOCATED ON BUILDING 4 FACING HWY 360- *BLOCKING AND POWER TO LOCATION BY OTHERS*</t>
+    <t>NON-ILLUMINATED PROJECT / LEASING ID - LOADS TO REAR ENTRY- OF LEASING ACCESS VIA AIRPORT PARKWAY ACCESS.</t>
+  </si>
+  <si>
+    <t>D.</t>
+  </si>
+  <si>
+    <t>WALL GRAPHIC ALLOWANCE FOR GARAGE ENTRY PORTAL- AND GARAGE WALLS. INCLUSIVE OF PROSPECT- PARKING IDENTIFICATION (BUDGETARY)</t>
+  </si>
+  <si>
+    <t>E.</t>
+  </si>
+  <si>
+    <t>MONUMENT STYLE SIGN AT CITY REQUIRED PARK BENCH- DIMENSIONAL GRAPHICS ON STRUCTURE BY OTHERS- LOCATED AT SW CORNER OF ADDISON ROAD</t>
   </si>
   <si>
     <t>#2: LEASING CENTER- EXTERIOR SIGNAGE</t>
   </si>
   <si>
-    <t>LEASING / PROJECT SINGLE - FACE NON - ILLUMINATED</t>
-  </si>
-  <si>
-    <t>HOURS SIGN W/ CHANGEABLE HOURS</t>
-  </si>
-  <si>
-    <t>ADDRESS NUMERALS - DIMENSIONAL</t>
-  </si>
-  <si>
-    <t>D.</t>
-  </si>
-  <si>
-    <t>CUSTOM HANDICAP PARKING W/BASEPLATE</t>
-  </si>
-  <si>
-    <t>E.</t>
-  </si>
-  <si>
-    <t>CUSTOM FUTURE RESIDENT PARKING SIGN W/BASEPLATE</t>
+    <t>LEASING CENTER ID - NON-ILLUMINATED 12" LETTERS ABOVE  ENTRY- LOADS TO CANOPY</t>
+  </si>
+  <si>
+    <t>ADDRESS ID - INDIVIDUAL NUMERALS</t>
+  </si>
+  <si>
+    <t>DOUBLE DOOR VINYL KIT (HOURS, LOGO, URL, PHONE)</t>
+  </si>
+  <si>
+    <t>"DOORS TO REMAIN UNLOCKED…" VINYL KIT</t>
+  </si>
+  <si>
+    <t>CUSTOM FUTURE RESIDENT PARKING SIGN - POST MOUNT- W/ BASEPLATE. PLACEMENT ON AIRPORT PKWY PARALLEL PARKING</t>
   </si>
   <si>
     <t>F.</t>
   </si>
   <si>
-    <t>USPS PARKING W/BASEPLATE</t>
+    <t>CUSTOM HANDICAP PARKING SIGN - POST MOUNT- W/ BASEPLATE. PLACEMENT ON AIRPORT PKWY PARALLEL PARKING</t>
   </si>
   <si>
     <t>G.</t>
   </si>
   <si>
-    <t>LOGO VINYL ON FRONT DOOR</t>
+    <t>CUSTOM USPS PARKING SIGN - WALL SIGN IN GARAGE</t>
   </si>
   <si>
     <t>H.</t>
   </si>
   <si>
-    <t>DOORS TO REMAIN UNLOCKED VINYL KIT</t>
+    <t>DELIVERY SIGN - 15 MIN. PARKING ON POST (VERIFY LOCATION)</t>
   </si>
   <si>
     <t xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </t>
   </si>
   <si>
-    <t>MANAGER ID W/BACKER</t>
-  </si>
-  <si>
-    <t>ASSISTANT MANAGER ID W/BACKER</t>
-  </si>
-  <si>
-    <t>EMPLOYEE ONLY (BREAK ROOM)</t>
-  </si>
-  <si>
-    <t>EMPLYEE ONLY (JANITOR)</t>
-  </si>
-  <si>
-    <t>CLUB ROOM ID W/BACKER</t>
+    <t>MANAGER ID W/ BACKER</t>
+  </si>
+  <si>
+    <t>ASST. MANAGER ID W/ BACKER</t>
+  </si>
+  <si>
+    <t>EMPLOYEE ONLY (WORKROOM)</t>
+  </si>
+  <si>
+    <t>MAIL ROOM ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </t>
+  </si>
+  <si>
+    <t>PARCEL STORAGE ID</t>
+  </si>
+  <si>
+    <t>IT ID</t>
+  </si>
+  <si>
+    <t>MDF ID (@FITNESS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITNESS ID </t>
+  </si>
+  <si>
+    <t>I.</t>
+  </si>
+  <si>
+    <t>FITNESS POLICY - WALL MOUNT</t>
+  </si>
+  <si>
+    <t>J.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEN'S RESTROOM </t>
+  </si>
+  <si>
+    <t>K.</t>
+  </si>
+  <si>
+    <t>WOMEN'S RESTROOM</t>
+  </si>
+  <si>
+    <t>L.</t>
+  </si>
+  <si>
+    <t>CLUB ROOM ID</t>
+  </si>
+  <si>
+    <t>M.</t>
   </si>
   <si>
     <t>CLUB ROOM POLICY - WALL MOUNT</t>
   </si>
   <si>
-    <t>CONFERENCE ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITNESS ID W/BACKER </t>
-  </si>
-  <si>
-    <t>I.</t>
-  </si>
-  <si>
-    <t>FITNESS CENTER POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>J.</t>
-  </si>
-  <si>
-    <t>SPIN / YOGA ID</t>
-  </si>
-  <si>
-    <t>K.</t>
-  </si>
-  <si>
-    <t>WOMENS RESTROOM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#3: LEASING CENTER - INTERIOR  SIGNAGE  </t>
-  </si>
-  <si>
-    <t>L.</t>
-  </si>
-  <si>
-    <t>MENS RESTROOM</t>
-  </si>
-  <si>
-    <t>M.</t>
-  </si>
-  <si>
-    <t>HVAC ID</t>
-  </si>
-  <si>
     <t>N.</t>
   </si>
   <si>
-    <t>MDF ID</t>
+    <t>UNIT ACCESS ID</t>
   </si>
   <si>
     <t>O.</t>
   </si>
   <si>
-    <t>MAX OCCUPANCY ( X1 LEASING, X1 CLUB, X1 AT FITNESS)</t>
+    <t>LEASING / AMENITY ACCESS ID</t>
   </si>
   <si>
     <t>P.</t>
   </si>
   <si>
-    <t>JPI DESKTOP PACKAGE (EQ HOUSING, ENG/SPAN, PROPER ID, NO CASH…)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#4: SITE SIGNAGE  </t>
+    <t>CO-WORK ID (@LVL5)</t>
+  </si>
+  <si>
+    <t>Q.</t>
+  </si>
+  <si>
+    <t>CO-WORK POLICY - WALL MOUNT (@LVL5)</t>
+  </si>
+  <si>
+    <t>R.</t>
+  </si>
+  <si>
+    <t>CO-WORK TERRACE ID</t>
+  </si>
+  <si>
+    <t>S.</t>
+  </si>
+  <si>
+    <t>UNISEX RESTROOM</t>
+  </si>
+  <si>
+    <t>T.</t>
+  </si>
+  <si>
+    <t>CONFERENCE ROOM ID</t>
+  </si>
+  <si>
+    <t>U.</t>
+  </si>
+  <si>
+    <t>CO-WORK POD ID</t>
+  </si>
+  <si>
+    <t>V.</t>
+  </si>
+  <si>
+    <t>MAX OCCUPANCY (LEASING, FITNESS, CLUB, CO-WORK, TERRACE)</t>
+  </si>
+  <si>
+    <t>W.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#4: PARKING GARAGE  - LEVEL 1 SIGNAGE </t>
   </si>
   <si>
     <t>ENTER / EXIT / GATE WARNING SIGN COMBO</t>
   </si>
   <si>
-    <t>TRASH COMPACTOR ID / POLICY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRASH / RECYCLE ENCLOSURE ID/POLICY </t>
-  </si>
-  <si>
-    <t>GARAGE BUILDING ID (X10 SINGLE, X16 DOUBLE)</t>
-  </si>
-  <si>
-    <t>DETACHED GARAGE DOOR NUMBER</t>
-  </si>
-  <si>
-    <t>CARPORTS NUMBERS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAIL KIOSK ID </t>
-  </si>
-  <si>
-    <t>EV CHARGING SIGN - ON POST (X3 HANDICAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#5: BUILDING #2 (TYPE II) SIGNAGE </t>
-  </si>
-  <si>
-    <t>BUILDING ID W/UNIT SPREAD</t>
-  </si>
-  <si>
-    <t>UNIT ACCESS (EXTERIOR)</t>
-  </si>
-  <si>
-    <t>UNIT NUMBER ( X20 AT LEVEL 1, X24 EACH AT LEVEL 2 / 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAIR ACCESS (EXTERIOR) </t>
-  </si>
-  <si>
-    <t>STAIR / LEVEL (X2 AT EACH LEVEL)</t>
-  </si>
-  <si>
-    <t>STORAGE ID (X15 AT LEVEL 1, X1 EACH AT LEVEL 2 / 3)</t>
-  </si>
-  <si>
-    <t>IDF ID (@LVL1)</t>
-  </si>
-  <si>
-    <t>ATTACHED GARAGE DOOR NUMBER (INTERIOR)</t>
-  </si>
-  <si>
-    <t>ATTACHED GARAGE DOOR NUMBER (EXTERIOR)</t>
-  </si>
-  <si>
-    <t>FIRE DOOR / DO NOT BLOCK ( X2 AT EACH LEVEL)</t>
-  </si>
-  <si>
-    <t>FIRE RISER (4")</t>
-  </si>
-  <si>
-    <t>FDC W / ADDRESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#6: BUILDING #3 (TYPE I) SIGNAGE </t>
-  </si>
-  <si>
-    <t>UNIT DOOR NUMBER (X24 AT EACH LEVEL)</t>
-  </si>
-  <si>
-    <t>STAIR ACCESS (EXTERIOR)</t>
-  </si>
-  <si>
-    <t>STORAGE ID (X7 AT LEVEL 1, X1 AT EACH LEVEL 2 / 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FIRE DOOR / DO NOT BLOCK </t>
-  </si>
-  <si>
-    <t xml:space="preserve">#7: BUILDING #4 (TYPE 1) SIGNAGE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">#8: BUILDING #5 (TYPE II) SIGNAGE </t>
-  </si>
-  <si>
-    <t>STAIR ACCESS (EXTERIOR )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#9: BUILDING #6 (TYPE IV) SIGNAGE </t>
-  </si>
-  <si>
-    <t>UNIT NUMBER (X6 AT LEVEL 1, X14 AT EACH LEVEL 2 / 3)</t>
-  </si>
-  <si>
-    <t>STORAGE ID (X18 AT LEVEL 1, X1 AT LEVEL 2, X2 AT LEVEL 3)</t>
-  </si>
-  <si>
-    <t>IDF ID (@ LVL2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#10: BUILDING #7 (TYPE III) SIGNAGE </t>
-  </si>
-  <si>
-    <t>UNIT NUMBER (X20 AT LEVEL 1, X24 AT EACH LEVEL 2 / 3)</t>
-  </si>
-  <si>
-    <t>STORAGE ID (X16 AT LEVEL 1, X1 AT EACH LEVEL 2 / 3)</t>
-  </si>
-  <si>
-    <t>FIRE DOOR / DO NOT BLOCK (X2 AT EACH LEVEL)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#11: BUILDING #8 (TYPE III) SIGNAGE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">#12: AMENITY SIGNAGE </t>
+    <t>CLEARANCE BAR PACKAGE (X1 @ EA. ENTRY, X1 @ GATE)</t>
+  </si>
+  <si>
+    <t>ELEVATOR EGRESS MAP / DO NOT USE</t>
+  </si>
+  <si>
+    <t>GARAGE TO BUILDING / STAIR / LEVEL / EXIT</t>
+  </si>
+  <si>
+    <t>STAIRWELL</t>
+  </si>
+  <si>
+    <t>GARAGE TO BUILDING (X1 @ EA. STAIR, X2 @ GARAGE NORTH ENTRY)</t>
+  </si>
+  <si>
+    <t>BUILDING TO GARAGE (X1 @ EA. STAIR, X1 @ ELEV. LOBBY)</t>
+  </si>
+  <si>
+    <t>TRASH PICK-UP / DO NOT BLOCK</t>
+  </si>
+  <si>
+    <t>EV CHARGING SIGN ALLOWANCE (LOCATION TBD) - WALL MOUNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#5: PARKING GARAGE - LEVEL 2 SIGNAGE </t>
+  </si>
+  <si>
+    <t>GARAGE TO BUILDING (X1@S3, X2@S2, X1 NEXT TO ELEVATOR)</t>
+  </si>
+  <si>
+    <t>BUILDING TO GARAGE (X1 @ EA. STAIR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESIDENT STORAGE ID </t>
+  </si>
+  <si>
+    <t>MAINTENANCE ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#6: PARKING GARAGE - LEVEL 3 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#7: PARKING GARAGE - LEVEL 4 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#8: PARKING GARAGE - LEVEL 5 SIGNAGE </t>
+  </si>
+  <si>
+    <t>GARAGE TO BUILDING / ELEVATOR LOBBY</t>
+  </si>
+  <si>
+    <t>BUILDING TO GARAGE (X1 @ EA. STAIR, X1 @ ELEV. EGRESS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#9: LEVEL 1 SIGNAGE </t>
+  </si>
+  <si>
+    <t>BUILDING ID W/ UNIT SPREAD</t>
+  </si>
+  <si>
+    <t>BUILDING ACCESS ID</t>
+  </si>
+  <si>
+    <t>HALLWAY DIRECTIONALS</t>
+  </si>
+  <si>
+    <t>UNIT DOOR NUMBERS</t>
+  </si>
+  <si>
+    <t>STAIR ACCESS (EXT) (S1)</t>
+  </si>
+  <si>
+    <t>BUILDING TO GARAGE / STAIR / LEVEL / EXIT (S3, S2)</t>
+  </si>
+  <si>
+    <t>STAIR / LEVEL / EXIT (S1)</t>
+  </si>
+  <si>
+    <t>STAIRWELL (S1)</t>
+  </si>
+  <si>
+    <t>ELEVATOR EGRESS MAP / DO NOT USE (E1, E3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUILDING TO GARAGE </t>
+  </si>
+  <si>
+    <t>MAINTENANCE ID (X2 @ NEXT TO FIRE RISER ROOM)</t>
+  </si>
+  <si>
+    <t>RESIDENT STORAGE ID</t>
+  </si>
+  <si>
+    <t>MECHANICAL ID</t>
+  </si>
+  <si>
+    <t>TRASH ROOM ID</t>
+  </si>
+  <si>
+    <t>TRASH ROOM POLICY - WALL MOUNT</t>
+  </si>
+  <si>
+    <t>FIRE DOOR / DO NOT BLOCK</t>
+  </si>
+  <si>
+    <t>FIRE RISER ROOM (4") - DIAMOND GRADE</t>
+  </si>
+  <si>
+    <t>FACP ID (VERIFY) - DIAMOND GRADE</t>
+  </si>
+  <si>
+    <t>FDC W/ ADDRESS - DIAMOND GRADE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#10: LEVEL 2 SIGNAGE </t>
+  </si>
+  <si>
+    <t>BUILDING TO GARAGE / STAIR / LEVEL / EXIT (X1@S3,X2@S2)</t>
+  </si>
+  <si>
+    <t>STAIR / LEVEL / EXIT (S1, S4)</t>
+  </si>
+  <si>
+    <t>STAIRWELL (S1, S4)</t>
+  </si>
+  <si>
+    <t>IDF ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#11: LEVEL 3 SIGNAGE </t>
+  </si>
+  <si>
+    <t>BUILDING TO GARAGE / STAIR / LEVEL / EXIT(X1@S3, X2@S2)</t>
+  </si>
+  <si>
+    <t>STAIR / LEVEL / EXIT(S1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#12: LEVEL 4 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#13: LEVEL 5 SIGNAGE </t>
+  </si>
+  <si>
+    <t>BUILDING TO GARAGE / STAIR / LEVEL / EXIT(X1@S3,X2@S2)</t>
+  </si>
+  <si>
+    <t>A/V ID</t>
+  </si>
+  <si>
+    <t>EMPLOYEE ONLY (JANITOR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#14: AMENITY SIGNAGE </t>
   </si>
   <si>
     <t>POOL POLICY</t>
@@ -334,16 +424,10 @@
     <t>POOL GATE W/ HOURS &amp; 911 DIRECTIONAL</t>
   </si>
   <si>
-    <t>GRILL POLICIES (X1 @ POOL, X1 @ DOG PARK)</t>
-  </si>
-  <si>
-    <t>PET PARK IDS (X1 LARGE, X1 SMALL) - GATE MOUNT</t>
-  </si>
-  <si>
-    <t>PET PARK POLICIES - FENCE MOUNT</t>
-  </si>
-  <si>
-    <t>FIRE PIT GUIDELINES PLAQUE (@POOL)</t>
+    <t>GRILL POLICIES (@POOL)</t>
+  </si>
+  <si>
+    <t>DESKTOP PACKAGE (PROPER ID, NO CASH, FAIR HOUSING, ON TOUR NO SMOKING, ETC.)</t>
   </si>
 </sst>
 </file>
@@ -720,14 +804,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="171.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="160.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -746,273 +834,279 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>16600</v>
+      </c>
+      <c r="F3">
+        <v>16600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4">
+        <v>6900</v>
+      </c>
+      <c r="F4">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>2950</v>
+      </c>
+      <c r="F5">
+        <v>2950</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6">
+        <v>8000</v>
+      </c>
+      <c r="F6">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>1800</v>
+      </c>
+      <c r="F7">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
-        <v>10900</v>
-      </c>
-      <c r="F3">
-        <v>10900</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>3600</v>
+      </c>
+      <c r="F8">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="E4">
-        <v>1265</v>
-      </c>
-      <c r="F4">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9">
+        <v>610</v>
+      </c>
+      <c r="F9">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
         <v>18</v>
       </c>
-      <c r="E5">
-        <v>11900</v>
-      </c>
-      <c r="F5">
-        <v>11900</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10">
+        <v>189</v>
+      </c>
+      <c r="F10">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
       </c>
-      <c r="E6">
-        <v>2800</v>
-      </c>
-      <c r="F6">
-        <v>2800</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7">
-        <v>410</v>
-      </c>
-      <c r="F7">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8">
-        <v>610</v>
-      </c>
-      <c r="F8">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9">
+      <c r="C11">
         <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9">
-        <v>715</v>
-      </c>
-      <c r="F9">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10">
-        <v>715</v>
-      </c>
-      <c r="F10">
-        <v>2145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>28</v>
       </c>
       <c r="E11">
-        <v>595</v>
+        <v>89</v>
       </c>
       <c r="F11">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="E12">
+        <v>715</v>
+      </c>
+      <c r="F12">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
         <v>30</v>
       </c>
-      <c r="E12">
-        <v>129</v>
-      </c>
-      <c r="F12">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
         <v>31</v>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="E13">
+        <v>715</v>
+      </c>
+      <c r="F13">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
         <v>32</v>
       </c>
-      <c r="E13">
-        <v>69</v>
-      </c>
-      <c r="F13">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
         <v>33</v>
       </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="E14">
+        <v>210</v>
+      </c>
+      <c r="F14">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" t="s">
         <v>34</v>
-      </c>
-      <c r="E14">
-        <v>68</v>
-      </c>
-      <c r="F14">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1021,104 +1115,104 @@
         <v>35</v>
       </c>
       <c r="E15">
-        <v>68</v>
+        <v>295</v>
       </c>
       <c r="F15">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F16">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="F17">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E18">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F18">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E19">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="F19">
-        <v>415</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E20">
         <v>48</v>
@@ -1129,50 +1223,50 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E21">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F21">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E22">
-        <v>415</v>
+        <v>48</v>
       </c>
       <c r="F22">
-        <v>415</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1181,15 +1275,15 @@
         <v>45</v>
       </c>
       <c r="E23">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F23">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
         <v>46</v>
@@ -1201,24 +1295,24 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>98</v>
+        <v>415</v>
       </c>
       <c r="F24">
-        <v>98</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
         <v>49</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" t="s">
-        <v>50</v>
       </c>
       <c r="E25">
         <v>98</v>
@@ -1229,110 +1323,110 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
         <v>51</v>
       </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>52</v>
-      </c>
       <c r="E26">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="F26">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
         <v>53</v>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="D27" t="s">
-        <v>54</v>
-      </c>
       <c r="E27">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F27">
-        <v>48</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
         <v>55</v>
       </c>
-      <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28" t="s">
-        <v>56</v>
-      </c>
       <c r="E28">
-        <v>58</v>
+        <v>415</v>
       </c>
       <c r="F28">
-        <v>174</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
         <v>57</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>58</v>
-      </c>
       <c r="E29">
-        <v>680</v>
+        <v>48</v>
       </c>
       <c r="F29">
-        <v>680</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
         <v>59</v>
       </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30">
-        <v>3</v>
-      </c>
-      <c r="D30" t="s">
-        <v>60</v>
-      </c>
       <c r="E30">
-        <v>335</v>
+        <v>48</v>
       </c>
       <c r="F30">
-        <v>1005</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1341,1324 +1435,1324 @@
         <v>61</v>
       </c>
       <c r="E31">
-        <v>185</v>
+        <v>78</v>
       </c>
       <c r="F31">
-        <v>370</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E32">
-        <v>155</v>
+        <v>415</v>
       </c>
       <c r="F32">
-        <v>465</v>
+        <v>415</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="C33">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E33">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="F33">
-        <v>4550</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C34">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E34">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="F34">
-        <v>5928</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C35">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E35">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F35">
-        <v>5928</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E36">
-        <v>185</v>
+        <v>48</v>
       </c>
       <c r="F36">
-        <v>370</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C37">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E37">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="F37">
-        <v>3685</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>69</v>
+        <v>135</v>
       </c>
       <c r="E38">
-        <v>310</v>
+        <v>680</v>
       </c>
       <c r="F38">
-        <v>1240</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E39">
-        <v>58</v>
+        <v>335</v>
       </c>
       <c r="F39">
-        <v>174</v>
+        <v>335</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C40">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E40">
-        <v>50</v>
+        <v>785</v>
       </c>
       <c r="F40">
-        <v>3400</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E41">
-        <v>58</v>
+        <v>245</v>
       </c>
       <c r="F41">
-        <v>116</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42">
+        <v>3</v>
+      </c>
+      <c r="D42" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42">
         <v>68</v>
       </c>
-      <c r="B42" t="s">
-        <v>25</v>
-      </c>
-      <c r="C42">
-        <v>6</v>
-      </c>
-      <c r="D42" t="s">
-        <v>73</v>
-      </c>
-      <c r="E42">
-        <v>48</v>
-      </c>
       <c r="F42">
-        <v>288</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C43">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E43">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="F43">
-        <v>816</v>
+        <v>495</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44">
+        <v>5</v>
+      </c>
+      <c r="D44" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44">
         <v>68</v>
       </c>
-      <c r="B44" t="s">
-        <v>29</v>
-      </c>
-      <c r="C44">
-        <v>2</v>
-      </c>
-      <c r="D44" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44">
-        <v>48</v>
-      </c>
       <c r="F44">
-        <v>96</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45">
         <v>68</v>
       </c>
-      <c r="B45" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45">
-        <v>9</v>
-      </c>
-      <c r="D45" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45">
-        <v>38</v>
-      </c>
       <c r="F45">
-        <v>342</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E46">
-        <v>38</v>
+        <v>285</v>
       </c>
       <c r="F46">
-        <v>342</v>
+        <v>570</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C47">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E47">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="F47">
-        <v>348</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E48">
-        <v>88</v>
+        <v>245</v>
       </c>
       <c r="F48">
-        <v>88</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>85</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49">
         <v>68</v>
       </c>
-      <c r="B49" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49" t="s">
-        <v>80</v>
-      </c>
-      <c r="E49">
-        <v>110</v>
-      </c>
       <c r="F49">
-        <v>110</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E50">
-        <v>310</v>
+        <v>165</v>
       </c>
       <c r="F50">
-        <v>1240</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="E51">
         <v>58</v>
       </c>
       <c r="F51">
-        <v>174</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C52">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E52">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F52">
-        <v>3600</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E53">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F53">
-        <v>116</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C54">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E54">
         <v>48</v>
       </c>
       <c r="F54">
-        <v>288</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C55">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E55">
-        <v>48</v>
+        <v>245</v>
       </c>
       <c r="F55">
-        <v>432</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C56">
         <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E56">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F56">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B57" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C57">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E57">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="F57">
-        <v>348</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E58">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="F58">
-        <v>88</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E59">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="F59">
-        <v>110</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="E60">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="F60">
-        <v>1240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D61" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E61">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F61">
-        <v>174</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C62">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E62">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="F62">
-        <v>3600</v>
+        <v>330</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
         <v>86</v>
-      </c>
-      <c r="B63" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63">
-        <v>2</v>
-      </c>
-      <c r="D63" t="s">
-        <v>83</v>
       </c>
       <c r="E63">
         <v>58</v>
       </c>
       <c r="F63">
-        <v>116</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C64">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D64" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E64">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F64">
-        <v>288</v>
+        <v>136</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C65">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D65" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E65">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F65">
-        <v>432</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E66">
-        <v>48</v>
+        <v>245</v>
       </c>
       <c r="F66">
-        <v>96</v>
+        <v>245</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B67" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C67">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E67">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="F67">
-        <v>348</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B68" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E68">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="F68">
-        <v>88</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
         <v>86</v>
       </c>
-      <c r="B69" t="s">
-        <v>44</v>
-      </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69" t="s">
-        <v>80</v>
-      </c>
       <c r="E69">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="F69">
-        <v>110</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="E70">
-        <v>310</v>
+        <v>68</v>
       </c>
       <c r="F70">
-        <v>1240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D71" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="E71">
-        <v>58</v>
+        <v>285</v>
       </c>
       <c r="F71">
-        <v>174</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C72">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="E72">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F72">
-        <v>3400</v>
+        <v>464</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D73" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E73">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="F73">
-        <v>116</v>
+        <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D74" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="E74">
         <v>48</v>
       </c>
       <c r="F74">
-        <v>288</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B75" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C75">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E75">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F75">
-        <v>816</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B76" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C76">
         <v>2</v>
       </c>
       <c r="D76" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="E76">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F76">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C77">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="E77">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F77">
-        <v>342</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B78" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C78">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E78">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="F78">
-        <v>342</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C79">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="E79">
-        <v>58</v>
+        <v>245</v>
       </c>
       <c r="F79">
-        <v>348</v>
+        <v>490</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="E80">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="F80">
-        <v>88</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="E81">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="F81">
-        <v>110</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="C82">
         <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="E82">
-        <v>310</v>
+        <v>48</v>
       </c>
       <c r="F82">
-        <v>1240</v>
+        <v>192</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D83" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="E83">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F83">
-        <v>116</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B84" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="C84">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="D84" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E84">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F84">
-        <v>1700</v>
+        <v>48</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E85">
-        <v>58</v>
+        <v>155</v>
       </c>
       <c r="F85">
-        <v>116</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B86" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C86">
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="E86">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F86">
-        <v>288</v>
+        <v>348</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C87">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="E87">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F87">
-        <v>1008</v>
+        <v>88</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E88">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F88">
-        <v>48</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="C89">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="E89">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="F89">
-        <v>608</v>
+        <v>110</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C90">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D90" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="E90">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F90">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="B91" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="D91" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E91">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F91">
-        <v>88</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="B92" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="E92">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="F92">
-        <v>110</v>
+        <v>204</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="E93">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="F93">
-        <v>1550</v>
+        <v>116</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="E94">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="F94">
-        <v>174</v>
+        <v>330</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B95" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C95">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E95">
-        <v>50</v>
+        <v>245</v>
       </c>
       <c r="F95">
-        <v>3400</v>
+        <v>490</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B96" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="E96">
         <v>58</v>
       </c>
       <c r="F96">
-        <v>116</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B97" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C97">
         <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="E97">
         <v>48</v>
@@ -2669,568 +2763,928 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B98" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C98">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E98">
         <v>48</v>
       </c>
       <c r="F98">
-        <v>864</v>
+        <v>144</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B99" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="E99">
         <v>48</v>
       </c>
       <c r="F99">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B100" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C100">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="E100">
-        <v>38</v>
+        <v>155</v>
       </c>
       <c r="F100">
-        <v>342</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C101">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="E101">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F101">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="B102" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C102">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E102">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="F102">
-        <v>348</v>
+        <v>600</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="B103" t="s">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="D103" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E103">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F103">
-        <v>88</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="B104" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="E104">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="F104">
-        <v>110</v>
+        <v>204</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="E105">
-        <v>310</v>
+        <v>58</v>
       </c>
       <c r="F105">
-        <v>1240</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="E106">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="F106">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B107" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C107">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E107">
-        <v>50</v>
+        <v>245</v>
       </c>
       <c r="F107">
-        <v>3400</v>
+        <v>490</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B108" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E108">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F108">
-        <v>116</v>
+        <v>288</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B109" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C109">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="E109">
         <v>48</v>
       </c>
       <c r="F109">
-        <v>288</v>
+        <v>144</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B110" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C110">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E110">
         <v>48</v>
       </c>
       <c r="F110">
-        <v>864</v>
+        <v>48</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B111" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="E111">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="F111">
-        <v>96</v>
+        <v>155</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="B112" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C112">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D112" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="E112">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F112">
-        <v>342</v>
+        <v>464</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B113" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="C113">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="E113">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="F113">
-        <v>342</v>
+        <v>600</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B114" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C114">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="D114" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E114">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F114">
-        <v>348</v>
+        <v>3024</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B115" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="E115">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F115">
-        <v>88</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
       <c r="D116" t="s">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="E116">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="F116">
-        <v>110</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E117">
-        <v>695</v>
+        <v>165</v>
       </c>
       <c r="F117">
-        <v>695</v>
+        <v>165</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="E118">
-        <v>410</v>
+        <v>245</v>
       </c>
       <c r="F118">
-        <v>410</v>
+        <v>490</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B119" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E119">
-        <v>410</v>
+        <v>48</v>
       </c>
       <c r="F119">
-        <v>410</v>
+        <v>288</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B120" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D120" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E120">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="F120">
-        <v>155</v>
+        <v>192</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B121" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C121">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E121">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="F121">
-        <v>620</v>
+        <v>48</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B122" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E122">
-        <v>335</v>
+        <v>48</v>
       </c>
       <c r="F122">
-        <v>670</v>
+        <v>48</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B123" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E123">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="F123">
-        <v>220</v>
+        <v>155</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D124" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E124">
-        <v>495</v>
+        <v>58</v>
       </c>
       <c r="F124">
-        <v>495</v>
+        <v>464</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125">
+        <v>5</v>
+      </c>
+      <c r="D125" t="s">
         <v>98</v>
       </c>
-      <c r="B125" t="s">
-        <v>42</v>
-      </c>
-      <c r="C125">
+      <c r="E125">
+        <v>120</v>
+      </c>
+      <c r="F125">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126">
+        <v>60</v>
+      </c>
+      <c r="D126" t="s">
+        <v>99</v>
+      </c>
+      <c r="E126">
+        <v>48</v>
+      </c>
+      <c r="F126">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>124</v>
+      </c>
+      <c r="B127" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127">
+        <v>3</v>
+      </c>
+      <c r="D127" t="s">
+        <v>125</v>
+      </c>
+      <c r="E127">
+        <v>68</v>
+      </c>
+      <c r="F127">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>124</v>
+      </c>
+      <c r="B128" t="s">
+        <v>20</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128" t="s">
+        <v>122</v>
+      </c>
+      <c r="E128">
+        <v>58</v>
+      </c>
+      <c r="F128">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>124</v>
+      </c>
+      <c r="B129" t="s">
+        <v>22</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="D129" t="s">
+        <v>103</v>
+      </c>
+      <c r="E129">
+        <v>165</v>
+      </c>
+      <c r="F129">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>124</v>
+      </c>
+      <c r="B130" t="s">
+        <v>30</v>
+      </c>
+      <c r="C130">
         <v>2</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D130" t="s">
+        <v>78</v>
+      </c>
+      <c r="E130">
+        <v>245</v>
+      </c>
+      <c r="F130">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>124</v>
+      </c>
+      <c r="B131" t="s">
+        <v>32</v>
+      </c>
+      <c r="C131">
+        <v>6</v>
+      </c>
+      <c r="D131" t="s">
         <v>107</v>
       </c>
-      <c r="E125">
-        <v>115</v>
-      </c>
-      <c r="F125">
-        <v>230</v>
+      <c r="E131">
+        <v>48</v>
+      </c>
+      <c r="F131">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>124</v>
+      </c>
+      <c r="B132" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132" t="s">
+        <v>126</v>
+      </c>
+      <c r="E132">
+        <v>48</v>
+      </c>
+      <c r="F132">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>124</v>
+      </c>
+      <c r="B133" t="s">
+        <v>46</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133" t="s">
+        <v>127</v>
+      </c>
+      <c r="E133">
+        <v>48</v>
+      </c>
+      <c r="F133">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>124</v>
+      </c>
+      <c r="B134" t="s">
+        <v>48</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134" t="s">
+        <v>108</v>
+      </c>
+      <c r="E134">
+        <v>48</v>
+      </c>
+      <c r="F134">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>124</v>
+      </c>
+      <c r="B135" t="s">
+        <v>50</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>109</v>
+      </c>
+      <c r="E135">
+        <v>48</v>
+      </c>
+      <c r="F135">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>124</v>
+      </c>
+      <c r="B136" t="s">
+        <v>52</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136" t="s">
+        <v>110</v>
+      </c>
+      <c r="E136">
+        <v>155</v>
+      </c>
+      <c r="F136">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>124</v>
+      </c>
+      <c r="B137" t="s">
+        <v>54</v>
+      </c>
+      <c r="C137">
+        <v>8</v>
+      </c>
+      <c r="D137" t="s">
+        <v>111</v>
+      </c>
+      <c r="E137">
+        <v>58</v>
+      </c>
+      <c r="F137">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>128</v>
+      </c>
+      <c r="B138" t="s">
+        <v>14</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138" t="s">
+        <v>129</v>
+      </c>
+      <c r="E138">
+        <v>695</v>
+      </c>
+      <c r="F138">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>128</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="D139" t="s">
+        <v>130</v>
+      </c>
+      <c r="E139">
+        <v>410</v>
+      </c>
+      <c r="F139">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>128</v>
+      </c>
+      <c r="B140" t="s">
+        <v>18</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140" t="s">
+        <v>131</v>
+      </c>
+      <c r="E140">
+        <v>410</v>
+      </c>
+      <c r="F140">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>128</v>
+      </c>
+      <c r="B141" t="s">
+        <v>20</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141" t="s">
+        <v>132</v>
+      </c>
+      <c r="E141">
+        <v>155</v>
+      </c>
+      <c r="F141">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>128</v>
+      </c>
+      <c r="B142" t="s">
+        <v>22</v>
+      </c>
+      <c r="C142">
+        <v>3</v>
+      </c>
+      <c r="D142" t="s">
+        <v>133</v>
+      </c>
+      <c r="E142">
+        <v>155</v>
+      </c>
+      <c r="F142">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>128</v>
+      </c>
+      <c r="B143" t="s">
+        <v>30</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143" t="s">
+        <v>134</v>
+      </c>
+      <c r="E143">
+        <v>335</v>
+      </c>
+      <c r="F143">
+        <v>335</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F125" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G37 A39:G143 A38:C38 E38:G38" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/010-npm_node/Testing_Book.xlsx
+++ b/010-npm_node/Testing_Book.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camdenbailey/Desktop/practice_notes/010-npm_node/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB9CBFF-C7B1-8349-AAF3-9A52AB797DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF716A88-33B0-F64B-A128-9D271FBE872F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="107">
   <si>
     <t>0</t>
   </si>
@@ -67,346 +67,253 @@
     <t>A.</t>
   </si>
   <si>
-    <t>ILLUMINATED BLADE SIGN LOADS ON NW CORNER OF ADDISON- ROAD ELEVATION. CHANNEL LETTERS &amp; PUSH-THRU ACRYLIC COPY.- *BLOCKING AND POWER TO LOCATION BY OTHERS*</t>
+    <t>DOUBLE FACE MONUMENT PER LANDSCAPE L2.01.- INCLUDES ADDRESS W/ DIMENSIONAL GRAPHICS (PER L4.02)- *STRUCTURE AND UPLIGHTING IN LANDSCAPE BY OTHERS*</t>
   </si>
   <si>
     <t>B.</t>
   </si>
   <si>
-    <t>ILLUMINATED PARKING BUTTON / PROJECTING SIGN AT GARAGE- ENTRY OFF AIRPORT PARKWAY.- *BLOCKING AND POWER TO LOCATION BY OTHERS*</t>
+    <t>SINGLE FACE MONUMENT LOCATED AT SECONDARY ENTRANCE- (PER CLIENT MARK-UPS) (FINAL DESIGN TBD)- *STRUCTURE AND UPLIGHTING IN LANDSCAPE BY OTHERS*</t>
+  </si>
+  <si>
+    <t>#2: LEASING CENTER- EXTERIOR SIGNAGE</t>
+  </si>
+  <si>
+    <t>LEASING CENTER ID - DIMENSIONAL LETTERS ON RAIL- FRONT LOADS TO FASCIA OVER LEASING ENTRY</t>
+  </si>
+  <si>
+    <t>ADDRESS ID - INDIVIDUAL NUMERALS - FACING PERSIMMON DR. ON BLDG 1</t>
   </si>
   <si>
     <t>C.</t>
   </si>
   <si>
-    <t>NON-ILLUMINATED PROJECT / LEASING ID - LOADS TO REAR ENTRY- OF LEASING ACCESS VIA AIRPORT PARKWAY ACCESS.</t>
+    <t>HOURS SIGN W/ CHANGEABLE HOURS</t>
   </si>
   <si>
     <t>D.</t>
   </si>
   <si>
-    <t>WALL GRAPHIC ALLOWANCE FOR GARAGE ENTRY PORTAL- AND GARAGE WALLS. INCLUSIVE OF PROSPECT- PARKING IDENTIFICATION (BUDGETARY)</t>
+    <t>DOUBLE DOOR VINYL KIT (LOGO, URL, PHONE)</t>
   </si>
   <si>
     <t>E.</t>
   </si>
   <si>
-    <t>MONUMENT STYLE SIGN AT CITY REQUIRED PARK BENCH- DIMENSIONAL GRAPHICS ON STRUCTURE BY OTHERS- LOCATED AT SW CORNER OF ADDISON ROAD</t>
-  </si>
-  <si>
-    <t>#2: LEASING CENTER- EXTERIOR SIGNAGE</t>
-  </si>
-  <si>
-    <t>LEASING CENTER ID - NON-ILLUMINATED 12" LETTERS ABOVE  ENTRY- LOADS TO CANOPY</t>
-  </si>
-  <si>
-    <t>ADDRESS ID - INDIVIDUAL NUMERALS</t>
-  </si>
-  <si>
-    <t>DOUBLE DOOR VINYL KIT (HOURS, LOGO, URL, PHONE)</t>
-  </si>
-  <si>
     <t>"DOORS TO REMAIN UNLOCKED…" VINYL KIT</t>
   </si>
   <si>
-    <t>CUSTOM FUTURE RESIDENT PARKING SIGN - POST MOUNT- W/ BASEPLATE. PLACEMENT ON AIRPORT PKWY PARALLEL PARKING</t>
-  </si>
-  <si>
     <t>F.</t>
   </si>
   <si>
-    <t>CUSTOM HANDICAP PARKING SIGN - POST MOUNT- W/ BASEPLATE. PLACEMENT ON AIRPORT PKWY PARALLEL PARKING</t>
+    <t>CUSTOM FUTURE RESIDENT PARKING SIGN - POLE MOUNT</t>
   </si>
   <si>
     <t>G.</t>
   </si>
   <si>
-    <t>CUSTOM USPS PARKING SIGN - WALL SIGN IN GARAGE</t>
+    <t>CUSTOM HANDICAP PARKING SIGN (X1 STD, X1 VAN) - POLE MOUNT</t>
   </si>
   <si>
     <t>H.</t>
   </si>
   <si>
-    <t>DELIVERY SIGN - 15 MIN. PARKING ON POST (VERIFY LOCATION)</t>
+    <t>CUSTOM USPS PARKING SIGN - POLE MOUNT</t>
+  </si>
+  <si>
+    <t>I.</t>
+  </si>
+  <si>
+    <t>CUSTOM EV CHARGING SIGN - POLE MOUNT</t>
+  </si>
+  <si>
+    <t>J.</t>
+  </si>
+  <si>
+    <t>DELIVERY / RIDESHARE PARKING SIGN - POLE MOUNT</t>
   </si>
   <si>
     <t xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </t>
   </si>
   <si>
-    <t>MANAGER ID W/ BACKER</t>
-  </si>
-  <si>
-    <t>ASST. MANAGER ID W/ BACKER</t>
-  </si>
-  <si>
-    <t>EMPLOYEE ONLY (WORKROOM)</t>
-  </si>
-  <si>
-    <t>MAIL ROOM ID</t>
+    <t>MANAGER ID W/ PVC BACKER</t>
+  </si>
+  <si>
+    <t>ASST. MANAGER ID W/ PVC BACKER</t>
+  </si>
+  <si>
+    <t>EMPLOYEE ONLY (X2 WORK ROOM, X1 JANITOR)</t>
+  </si>
+  <si>
+    <t>MAIL ROOM ID (X1 EXT, X1 INT)</t>
+  </si>
+  <si>
+    <t>PACKAGE ID</t>
+  </si>
+  <si>
+    <t>LEASING ID (X1 W/ MAX OCC)</t>
+  </si>
+  <si>
+    <t>CLUB ROOM ID (W/ MAX OCC)</t>
+  </si>
+  <si>
+    <t>CLUB ROOM POLICY - WALL MOUNT</t>
+  </si>
+  <si>
+    <t>MEN'S RESTROOM ID</t>
+  </si>
+  <si>
+    <t>WOMEN'S RESTROOM ID</t>
+  </si>
+  <si>
+    <t>K.</t>
+  </si>
+  <si>
+    <t>FITNESS ID (W/ MAX OCC)</t>
   </si>
   <si>
     <t xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </t>
   </si>
   <si>
-    <t>PARCEL STORAGE ID</t>
-  </si>
-  <si>
-    <t>IT ID</t>
-  </si>
-  <si>
-    <t>MDF ID (@FITNESS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FITNESS ID </t>
-  </si>
-  <si>
-    <t>I.</t>
+    <t>L.</t>
   </si>
   <si>
     <t>FITNESS POLICY - WALL MOUNT</t>
   </si>
   <si>
-    <t>J.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEN'S RESTROOM </t>
-  </si>
-  <si>
-    <t>K.</t>
-  </si>
-  <si>
-    <t>WOMEN'S RESTROOM</t>
-  </si>
-  <si>
-    <t>L.</t>
-  </si>
-  <si>
-    <t>CLUB ROOM ID</t>
-  </si>
-  <si>
     <t>M.</t>
   </si>
   <si>
-    <t>CLUB ROOM POLICY - WALL MOUNT</t>
+    <t>YOGA ID</t>
   </si>
   <si>
     <t>N.</t>
   </si>
   <si>
-    <t>UNIT ACCESS ID</t>
+    <t>MECHANICAL ID (X1 @ CLUB)</t>
   </si>
   <si>
     <t>O.</t>
   </si>
   <si>
-    <t>LEASING / AMENITY ACCESS ID</t>
+    <t>MDF ID</t>
   </si>
   <si>
     <t>P.</t>
   </si>
   <si>
-    <t>CO-WORK ID (@LVL5)</t>
-  </si>
-  <si>
     <t>Q.</t>
   </si>
   <si>
-    <t>CO-WORK POLICY - WALL MOUNT (@LVL5)</t>
-  </si>
-  <si>
-    <t>R.</t>
-  </si>
-  <si>
-    <t>CO-WORK TERRACE ID</t>
-  </si>
-  <si>
-    <t>S.</t>
-  </si>
-  <si>
-    <t>UNISEX RESTROOM</t>
-  </si>
-  <si>
-    <t>T.</t>
-  </si>
-  <si>
-    <t>CONFERENCE ROOM ID</t>
-  </si>
-  <si>
-    <t>U.</t>
-  </si>
-  <si>
-    <t>CO-WORK POD ID</t>
-  </si>
-  <si>
-    <t>V.</t>
-  </si>
-  <si>
-    <t>MAX OCCUPANCY (LEASING, FITNESS, CLUB, CO-WORK, TERRACE)</t>
-  </si>
-  <si>
-    <t>W.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#4: PARKING GARAGE  - LEVEL 1 SIGNAGE </t>
+    <t>MAX OCCUPANCY (LOBBY, LEASE, FITNESS , CLUB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#4: SITE SIGNAGE </t>
+  </si>
+  <si>
+    <t>MONOLITHIC DIRECTIONAL (PER CLIENT MARK-UP)</t>
+  </si>
+  <si>
+    <t>SITE DIRECTORY - POST &amp; PANEL W/ DIGITALLY PRINTED SITE PLAN- LOCATED AT EACH VISITOR ENTRY MEDIAN AT CALL BOXES</t>
+  </si>
+  <si>
+    <t>CARPORT ID (X2 HCP) (PER A000) ("C" - 100, 101, 102, ETC.)</t>
   </si>
   <si>
     <t>ENTER / EXIT / GATE WARNING SIGN COMBO</t>
   </si>
   <si>
-    <t>CLEARANCE BAR PACKAGE (X1 @ EA. ENTRY, X1 @ GATE)</t>
+    <t>TRASH ENCLOSURE ID / POLICY / DO NOT BLOCK</t>
+  </si>
+  <si>
+    <t>MAIL KIOSK ID</t>
+  </si>
+  <si>
+    <t>TOWNHOME UNIT DOOR NUMBERS at 4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#5: BUILDING MF-1 LEVEL BASEMENT SIGNAGE </t>
+  </si>
+  <si>
+    <t>BUILDING ID W/ UNIT SPREAD</t>
+  </si>
+  <si>
+    <t>BUILDING ACCESS ID</t>
+  </si>
+  <si>
+    <t>UNIT DOOR NUMBERS ("BUILDING #, FLOOR LEVEL")</t>
+  </si>
+  <si>
+    <t>STAIR / LEVEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAIRWELL </t>
   </si>
   <si>
     <t>ELEVATOR EGRESS MAP / DO NOT USE</t>
   </si>
   <si>
-    <t>GARAGE TO BUILDING / STAIR / LEVEL / EXIT</t>
+    <t>RESIDENT STORAGE ID ("S" - BUILDING #, FLOOR LEVEL, 01, 02, ETC.)</t>
+  </si>
+  <si>
+    <t>FIRE DOOR / DO NOT BLOCK</t>
+  </si>
+  <si>
+    <t>FACP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#6: BUILDING MF-1 LEVEL 1 SIGNAGE </t>
+  </si>
+  <si>
+    <t>HALLWAY DIRECTIONAL</t>
   </si>
   <si>
     <t>STAIRWELL</t>
   </si>
   <si>
-    <t>GARAGE TO BUILDING (X1 @ EA. STAIR, X2 @ GARAGE NORTH ENTRY)</t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE (X1 @ EA. STAIR, X1 @ ELEV. LOBBY)</t>
-  </si>
-  <si>
-    <t>TRASH PICK-UP / DO NOT BLOCK</t>
-  </si>
-  <si>
-    <t>EV CHARGING SIGN ALLOWANCE (LOCATION TBD) - WALL MOUNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#5: PARKING GARAGE - LEVEL 2 SIGNAGE </t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING (X1@S3, X2@S2, X1 NEXT TO ELEVATOR)</t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE (X1 @ EA. STAIR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESIDENT STORAGE ID </t>
+    <t>IDF ID</t>
+  </si>
+  <si>
+    <t>FIRE DOOR / DO NOT USE</t>
+  </si>
+  <si>
+    <t>FSRR (4")</t>
+  </si>
+  <si>
+    <t>FDC W/ ADDRESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#7: BUILDING MF-1 LEVEL 2 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#8: BUILDING MF-1 LEVEL 3 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#9: BUILDING MF-1 LEVEL 4 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#10: BUILDING MF-2 LEVEL 1 SIGNAGE </t>
+  </si>
+  <si>
+    <t>MECHANICAL ID</t>
   </si>
   <si>
     <t>MAINTENANCE ID</t>
   </si>
   <si>
-    <t xml:space="preserve">#6: PARKING GARAGE - LEVEL 3 SIGNAGE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">#7: PARKING GARAGE - LEVEL 4 SIGNAGE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">#8: PARKING GARAGE - LEVEL 5 SIGNAGE </t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING / ELEVATOR LOBBY</t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE (X1 @ EA. STAIR, X1 @ ELEV. EGRESS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#9: LEVEL 1 SIGNAGE </t>
-  </si>
-  <si>
-    <t>BUILDING ID W/ UNIT SPREAD</t>
-  </si>
-  <si>
-    <t>BUILDING ACCESS ID</t>
-  </si>
-  <si>
-    <t>HALLWAY DIRECTIONALS</t>
-  </si>
-  <si>
-    <t>UNIT DOOR NUMBERS</t>
-  </si>
-  <si>
-    <t>STAIR ACCESS (EXT) (S1)</t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / STAIR / LEVEL / EXIT (S3, S2)</t>
-  </si>
-  <si>
-    <t>STAIR / LEVEL / EXIT (S1)</t>
-  </si>
-  <si>
-    <t>STAIRWELL (S1)</t>
-  </si>
-  <si>
-    <t>ELEVATOR EGRESS MAP / DO NOT USE (E1, E3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUILDING TO GARAGE </t>
-  </si>
-  <si>
-    <t>MAINTENANCE ID (X2 @ NEXT TO FIRE RISER ROOM)</t>
-  </si>
-  <si>
-    <t>RESIDENT STORAGE ID</t>
-  </si>
-  <si>
-    <t>MECHANICAL ID</t>
-  </si>
-  <si>
-    <t>TRASH ROOM ID</t>
-  </si>
-  <si>
-    <t>TRASH ROOM POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>FIRE DOOR / DO NOT BLOCK</t>
-  </si>
-  <si>
-    <t>FIRE RISER ROOM (4") - DIAMOND GRADE</t>
-  </si>
-  <si>
-    <t>FACP ID (VERIFY) - DIAMOND GRADE</t>
-  </si>
-  <si>
-    <t>FDC W/ ADDRESS - DIAMOND GRADE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#10: LEVEL 2 SIGNAGE </t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / STAIR / LEVEL / EXIT (X1@S3,X2@S2)</t>
-  </si>
-  <si>
-    <t>STAIR / LEVEL / EXIT (S1, S4)</t>
-  </si>
-  <si>
-    <t>STAIRWELL (S1, S4)</t>
-  </si>
-  <si>
-    <t>IDF ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#11: LEVEL 3 SIGNAGE </t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / STAIR / LEVEL / EXIT(X1@S3, X2@S2)</t>
-  </si>
-  <si>
-    <t>STAIR / LEVEL / EXIT(S1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#12: LEVEL 4 SIGNAGE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">#13: LEVEL 5 SIGNAGE </t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / STAIR / LEVEL / EXIT(X1@S3,X2@S2)</t>
-  </si>
-  <si>
-    <t>A/V ID</t>
-  </si>
-  <si>
-    <t>EMPLOYEE ONLY (JANITOR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#14: AMENITY SIGNAGE </t>
+    <t xml:space="preserve">#11: BUILDING MF-2 LEVEL 2 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#12: BUILDING MF-2 LEVEL 3 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#13: BUILDING MF-2 LEVEL 4 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#14: BUILDING MF-3 SIGNAGE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#15: AMENITY SIGNAGE </t>
   </si>
   <si>
     <t>POOL POLICY</t>
@@ -424,10 +331,16 @@
     <t>POOL GATE W/ HOURS &amp; 911 DIRECTIONAL</t>
   </si>
   <si>
-    <t>GRILL POLICIES (@POOL)</t>
+    <t>OUTDOOR KITCHEN POLICIES (X1 @ POOL, X1 @ POD 4 COURTYARD)</t>
+  </si>
+  <si>
+    <t>DOG PARK ID / POLICY</t>
   </si>
   <si>
     <t>DESKTOP PACKAGE (PROPER ID, NO CASH, FAIR HOUSING, ON TOUR NO SMOKING, ETC.)</t>
+  </si>
+  <si>
+    <t>UNIT DOOR NUMBERS (X19@ EACH LEVEL) ("BUILDING #, FLOOR LEVEL")</t>
   </si>
 </sst>
 </file>
@@ -804,15 +717,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="160.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="149.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -875,10 +786,10 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>16600</v>
+        <v>7800</v>
       </c>
       <c r="F3">
-        <v>16600</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -895,18 +806,18 @@
         <v>17</v>
       </c>
       <c r="E4">
-        <v>6900</v>
+        <v>4400</v>
       </c>
       <c r="F4">
-        <v>6900</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -915,78 +826,78 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>2950</v>
+        <v>3400</v>
       </c>
       <c r="F5">
-        <v>2950</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
       <c r="E6">
-        <v>8000</v>
+        <v>385</v>
       </c>
       <c r="F6">
-        <v>8000</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
         <v>22</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
       <c r="E7">
-        <v>1800</v>
+        <v>410</v>
       </c>
       <c r="F7">
-        <v>1800</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
         <v>24</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
       <c r="E8">
-        <v>3600</v>
+        <v>129</v>
       </c>
       <c r="F8">
-        <v>3600</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -995,298 +906,298 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>610</v>
+        <v>89</v>
       </c>
       <c r="F9">
-        <v>610</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10">
-        <v>189</v>
+        <v>715</v>
       </c>
       <c r="F10">
-        <v>378</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E11">
-        <v>89</v>
+        <v>715</v>
       </c>
       <c r="F11">
-        <v>178</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12">
-        <v>715</v>
+        <v>595</v>
       </c>
       <c r="F12">
-        <v>2145</v>
+        <v>595</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E13">
-        <v>715</v>
+        <v>495</v>
       </c>
       <c r="F13">
-        <v>715</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E14">
-        <v>210</v>
+        <v>715</v>
       </c>
       <c r="F14">
-        <v>210</v>
+        <v>715</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E15">
-        <v>295</v>
+        <v>68</v>
       </c>
       <c r="F15">
-        <v>295</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F16">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E17">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="F17">
-        <v>78</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E18">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="F18">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E19">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F19">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F20">
-        <v>48</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F21">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22">
-        <v>48</v>
+        <v>415</v>
       </c>
       <c r="F22">
-        <v>48</v>
+        <v>415</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E23">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="F23">
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1295,15 +1206,15 @@
         <v>47</v>
       </c>
       <c r="E24">
-        <v>415</v>
+        <v>98</v>
       </c>
       <c r="F24">
-        <v>415</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
         <v>48</v>
@@ -1315,584 +1226,584 @@
         <v>49</v>
       </c>
       <c r="E25">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="F25">
-        <v>98</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E26">
-        <v>98</v>
+        <v>415</v>
       </c>
       <c r="F26">
-        <v>98</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E27">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F27">
-        <v>156</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E28">
-        <v>415</v>
+        <v>48</v>
       </c>
       <c r="F28">
-        <v>415</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E29">
         <v>48</v>
       </c>
       <c r="F29">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="E30">
-        <v>48</v>
+        <v>680</v>
       </c>
       <c r="F30">
-        <v>96</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
         <v>60</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
         <v>61</v>
       </c>
       <c r="E31">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F31">
-        <v>156</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
         <v>63</v>
       </c>
       <c r="E32">
-        <v>415</v>
+        <v>895</v>
       </c>
       <c r="F32">
-        <v>415</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="C33">
         <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E33">
-        <v>78</v>
+        <v>2195</v>
       </c>
       <c r="F33">
-        <v>156</v>
+        <v>4390</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="D34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E34">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="F34">
-        <v>98</v>
+        <v>9760</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E35">
-        <v>48</v>
+        <v>310</v>
       </c>
       <c r="F35">
-        <v>48</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E36">
-        <v>48</v>
+        <v>185</v>
       </c>
       <c r="F36">
-        <v>48</v>
+        <v>555</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E37">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="F37">
-        <v>290</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38">
         <v>74</v>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="E38">
-        <v>680</v>
+        <v>88</v>
       </c>
       <c r="F38">
-        <v>680</v>
+        <v>6512</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
         <v>14</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D39" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E39">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="F39">
-        <v>335</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
         <v>16</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E40">
-        <v>785</v>
+        <v>48</v>
       </c>
       <c r="F40">
-        <v>2355</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E41">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="F41">
-        <v>245</v>
+        <v>624</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E42">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F42">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43" t="s">
         <v>75</v>
       </c>
-      <c r="B43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43">
-        <v>3</v>
-      </c>
-      <c r="D43" t="s">
-        <v>80</v>
-      </c>
       <c r="E43">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="F43">
-        <v>495</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C44">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E44">
-        <v>68</v>
+        <v>245</v>
       </c>
       <c r="F44">
-        <v>340</v>
+        <v>245</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D45" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E45">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F45">
-        <v>272</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
       <c r="D46" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E46">
-        <v>285</v>
+        <v>58</v>
       </c>
       <c r="F46">
-        <v>570</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E47">
         <v>110</v>
       </c>
       <c r="F47">
-        <v>1100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E48">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="F48">
-        <v>245</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B49" t="s">
         <v>16</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E49">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F49">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E50">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="F50">
-        <v>330</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E51">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="F51">
-        <v>232</v>
+        <v>495</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E52">
-        <v>68</v>
+        <v>210</v>
       </c>
       <c r="F52">
-        <v>136</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E53">
         <v>48</v>
       </c>
       <c r="F53">
-        <v>144</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E54">
         <v>48</v>
@@ -1903,896 +1814,896 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E55">
-        <v>245</v>
+        <v>58</v>
       </c>
       <c r="F55">
-        <v>245</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E56">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="F56">
-        <v>136</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E57">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="F57">
-        <v>330</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E58">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F58">
-        <v>232</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E59">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F59">
-        <v>136</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E60">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="F60">
-        <v>245</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E61">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="F61">
-        <v>136</v>
+        <v>495</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E62">
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="F62">
-        <v>330</v>
+        <v>210</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E63">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F63">
-        <v>232</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B64" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E64">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F64">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B65" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="E65">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F65">
-        <v>68</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D66" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E66">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="F66">
-        <v>245</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B67" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E67">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F67">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E68">
         <v>165</v>
       </c>
       <c r="F68">
-        <v>330</v>
+        <v>495</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B69" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E69">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="F69">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D70" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E70">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="F70">
-        <v>204</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C71">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D71" t="s">
+        <v>83</v>
+      </c>
+      <c r="E71">
+        <v>48</v>
+      </c>
+      <c r="F71">
         <v>96</v>
-      </c>
-      <c r="E71">
-        <v>285</v>
-      </c>
-      <c r="F71">
-        <v>1425</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C72">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E72">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F72">
-        <v>464</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B73" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D73" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E73">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="F73">
-        <v>600</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B74" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C74">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="E74">
         <v>48</v>
       </c>
       <c r="F74">
-        <v>2352</v>
+        <v>864</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="E75">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F75">
-        <v>58</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C76">
         <v>2</v>
       </c>
       <c r="D76" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="E76">
-        <v>68</v>
+        <v>165</v>
       </c>
       <c r="F76">
-        <v>136</v>
+        <v>330</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C77">
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="E77">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="F77">
-        <v>58</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B78" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C78">
         <v>1</v>
       </c>
       <c r="D78" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="E78">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="F78">
-        <v>165</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E79">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="F79">
-        <v>490</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B80" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C80">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E80">
-        <v>58</v>
+        <v>285</v>
       </c>
       <c r="F80">
-        <v>232</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="E81">
         <v>48</v>
       </c>
       <c r="F81">
-        <v>144</v>
+        <v>912</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B82" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D82" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="E82">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F82">
-        <v>192</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E83">
         <v>48</v>
       </c>
       <c r="F83">
-        <v>48</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E84">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="F84">
-        <v>48</v>
+        <v>330</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="E85">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="F85">
-        <v>155</v>
+        <v>210</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C86">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E86">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F86">
-        <v>348</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B87" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C87">
         <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="E87">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F87">
-        <v>88</v>
+        <v>48</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E88">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F88">
-        <v>88</v>
+        <v>48</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C89">
         <v>1</v>
       </c>
       <c r="D89" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="E89">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="F89">
-        <v>110</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C90">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E90">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F90">
-        <v>600</v>
+        <v>110</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C91">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E91">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="F91">
-        <v>2784</v>
+        <v>110</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B92" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C92">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D92" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="E92">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F92">
-        <v>204</v>
+        <v>912</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D93" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="E93">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="F93">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="E94">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="F94">
-        <v>330</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E95">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="F95">
-        <v>490</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B96" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C96">
         <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="E96">
-        <v>58</v>
+        <v>210</v>
       </c>
       <c r="F96">
-        <v>58</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C97">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="E97">
         <v>48</v>
       </c>
       <c r="F97">
-        <v>288</v>
+        <v>48</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B98" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="E98">
         <v>48</v>
       </c>
       <c r="F98">
-        <v>144</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B99" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="E99">
         <v>48</v>
@@ -2803,888 +2714,588 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B100" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C100">
         <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="E100">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="F100">
-        <v>155</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="B101" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C101">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D101" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="E101">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F101">
-        <v>348</v>
+        <v>912</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B102" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E102">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="F102">
-        <v>600</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B103" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C103">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E103">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="F103">
-        <v>3024</v>
+        <v>330</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B104" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="E104">
-        <v>68</v>
+        <v>210</v>
       </c>
       <c r="F104">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B105" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C105">
         <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="E105">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="F105">
-        <v>58</v>
+        <v>110</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B106" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C106">
         <v>1</v>
       </c>
       <c r="D106" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E106">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="F106">
-        <v>165</v>
+        <v>48</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="B107" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E107">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="F107">
-        <v>490</v>
+        <v>144</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B108" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C108">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D108" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="E108">
         <v>48</v>
       </c>
       <c r="F108">
-        <v>288</v>
+        <v>912</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E109">
         <v>48</v>
       </c>
       <c r="F109">
-        <v>144</v>
+        <v>96</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B110" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E110">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="F110">
-        <v>48</v>
+        <v>330</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B111" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C111">
         <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="E111">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="F111">
-        <v>155</v>
+        <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="B112" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C112">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D112" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="E112">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="F112">
-        <v>464</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="B113" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C113">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E113">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="F113">
-        <v>600</v>
+        <v>48</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="B114" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C114">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E114">
         <v>48</v>
       </c>
       <c r="F114">
-        <v>3024</v>
+        <v>48</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="B115" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C115">
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="E115">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="F115">
-        <v>204</v>
+        <v>144</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B116" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D116" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E116">
-        <v>58</v>
+        <v>285</v>
       </c>
       <c r="F116">
-        <v>58</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B117" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="D117" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E117">
-        <v>165</v>
+        <v>48</v>
       </c>
       <c r="F117">
-        <v>165</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E118">
-        <v>245</v>
+        <v>48</v>
       </c>
       <c r="F118">
-        <v>490</v>
+        <v>96</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B119" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C119">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="E119">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="F119">
-        <v>288</v>
+        <v>88</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B120" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D120" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="E120">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="F120">
-        <v>192</v>
+        <v>110</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B121" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E121">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="F121">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="B122" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C122">
         <v>1</v>
       </c>
       <c r="D122" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E122">
-        <v>48</v>
+        <v>715</v>
       </c>
       <c r="F122">
-        <v>48</v>
+        <v>715</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="B123" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C123">
         <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E123">
-        <v>155</v>
+        <v>410</v>
       </c>
       <c r="F123">
-        <v>155</v>
+        <v>410</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="B124" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C124">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="E124">
-        <v>58</v>
+        <v>410</v>
       </c>
       <c r="F124">
-        <v>464</v>
+        <v>410</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C125">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E125">
-        <v>120</v>
+        <v>155</v>
       </c>
       <c r="F125">
-        <v>600</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="B126" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C126">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="D126" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E126">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="F126">
-        <v>2880</v>
+        <v>775</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C127">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="E127">
-        <v>68</v>
+        <v>365</v>
       </c>
       <c r="F127">
-        <v>204</v>
+        <v>730</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="B128" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C128">
         <v>1</v>
       </c>
       <c r="D128" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E128">
-        <v>58</v>
+        <v>595</v>
       </c>
       <c r="F128">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>124</v>
-      </c>
-      <c r="B129" t="s">
-        <v>22</v>
-      </c>
-      <c r="C129">
-        <v>1</v>
-      </c>
-      <c r="D129" t="s">
-        <v>103</v>
-      </c>
-      <c r="E129">
-        <v>165</v>
-      </c>
-      <c r="F129">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
-        <v>124</v>
-      </c>
-      <c r="B130" t="s">
-        <v>30</v>
-      </c>
-      <c r="C130">
-        <v>2</v>
-      </c>
-      <c r="D130" t="s">
-        <v>78</v>
-      </c>
-      <c r="E130">
-        <v>245</v>
-      </c>
-      <c r="F130">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
-        <v>124</v>
-      </c>
-      <c r="B131" t="s">
-        <v>32</v>
-      </c>
-      <c r="C131">
-        <v>6</v>
-      </c>
-      <c r="D131" t="s">
-        <v>107</v>
-      </c>
-      <c r="E131">
-        <v>48</v>
-      </c>
-      <c r="F131">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>124</v>
-      </c>
-      <c r="B132" t="s">
-        <v>34</v>
-      </c>
-      <c r="C132">
-        <v>1</v>
-      </c>
-      <c r="D132" t="s">
-        <v>126</v>
-      </c>
-      <c r="E132">
-        <v>48</v>
-      </c>
-      <c r="F132">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>124</v>
-      </c>
-      <c r="B133" t="s">
-        <v>46</v>
-      </c>
-      <c r="C133">
-        <v>1</v>
-      </c>
-      <c r="D133" t="s">
-        <v>127</v>
-      </c>
-      <c r="E133">
-        <v>48</v>
-      </c>
-      <c r="F133">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>124</v>
-      </c>
-      <c r="B134" t="s">
-        <v>48</v>
-      </c>
-      <c r="C134">
-        <v>1</v>
-      </c>
-      <c r="D134" t="s">
-        <v>108</v>
-      </c>
-      <c r="E134">
-        <v>48</v>
-      </c>
-      <c r="F134">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>124</v>
-      </c>
-      <c r="B135" t="s">
-        <v>50</v>
-      </c>
-      <c r="C135">
-        <v>1</v>
-      </c>
-      <c r="D135" t="s">
-        <v>109</v>
-      </c>
-      <c r="E135">
-        <v>48</v>
-      </c>
-      <c r="F135">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>124</v>
-      </c>
-      <c r="B136" t="s">
-        <v>52</v>
-      </c>
-      <c r="C136">
-        <v>1</v>
-      </c>
-      <c r="D136" t="s">
-        <v>110</v>
-      </c>
-      <c r="E136">
-        <v>155</v>
-      </c>
-      <c r="F136">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>124</v>
-      </c>
-      <c r="B137" t="s">
-        <v>54</v>
-      </c>
-      <c r="C137">
-        <v>8</v>
-      </c>
-      <c r="D137" t="s">
-        <v>111</v>
-      </c>
-      <c r="E137">
-        <v>58</v>
-      </c>
-      <c r="F137">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>128</v>
-      </c>
-      <c r="B138" t="s">
-        <v>14</v>
-      </c>
-      <c r="C138">
-        <v>1</v>
-      </c>
-      <c r="D138" t="s">
-        <v>129</v>
-      </c>
-      <c r="E138">
-        <v>695</v>
-      </c>
-      <c r="F138">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>128</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139">
-        <v>1</v>
-      </c>
-      <c r="D139" t="s">
-        <v>130</v>
-      </c>
-      <c r="E139">
-        <v>410</v>
-      </c>
-      <c r="F139">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>128</v>
-      </c>
-      <c r="B140" t="s">
-        <v>18</v>
-      </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-      <c r="D140" t="s">
-        <v>131</v>
-      </c>
-      <c r="E140">
-        <v>410</v>
-      </c>
-      <c r="F140">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>128</v>
-      </c>
-      <c r="B141" t="s">
-        <v>20</v>
-      </c>
-      <c r="C141">
-        <v>1</v>
-      </c>
-      <c r="D141" t="s">
-        <v>132</v>
-      </c>
-      <c r="E141">
-        <v>155</v>
-      </c>
-      <c r="F141">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>128</v>
-      </c>
-      <c r="B142" t="s">
-        <v>22</v>
-      </c>
-      <c r="C142">
-        <v>3</v>
-      </c>
-      <c r="D142" t="s">
-        <v>133</v>
-      </c>
-      <c r="E142">
-        <v>155</v>
-      </c>
-      <c r="F142">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>128</v>
-      </c>
-      <c r="B143" t="s">
-        <v>30</v>
-      </c>
-      <c r="C143">
-        <v>1</v>
-      </c>
-      <c r="D143" t="s">
-        <v>134</v>
-      </c>
-      <c r="E143">
-        <v>335</v>
-      </c>
-      <c r="F143">
-        <v>335</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G37 A39:G143 A38:C38 E38:G38" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G29 A31:G116 A30:C30 E30:G30 A118:G128 A117:C117 E117:G117" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/010-npm_node/Testing_Book.xlsx
+++ b/010-npm_node/Testing_Book.xlsx
@@ -1,563 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camdenbailey/Desktop/practice_notes/010-npm_node/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DC10A3-4BFF-A449-8CDE-FB94A2C1AE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Testing-00" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="177">
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>SECTION_ID</t>
-  </si>
-  <si>
-    <t>SPOTTING_KEY</t>
-  </si>
-  <si>
-    <t>SIGN_COUNT</t>
-  </si>
-  <si>
-    <t>SIGN_DESCRIPTION</t>
-  </si>
-  <si>
-    <t>EACH_COST</t>
-  </si>
-  <si>
-    <t>TOTAL_COST</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>#1: ENTRY SIGNAGE</t>
-  </si>
-  <si>
-    <t>A.</t>
-  </si>
-  <si>
-    <t>ILLUMINATED DOUBLE-FACED BLADE / PROJECTING SIGNS. CUSTOM "C"- CHANNEL LETTERS W/PUSH - THRU ARCYLIC. FEATURES LED TUBE LIGHTING- ON TWO SIDES. LOADS TO ARMATURE BRACKET FURNISHED BY FOURCE.- LOADS TO BLOCKING PRIOR TO FASCIA / BRICK APPLICATION- *BLOCKING AND POWER TO LOCATION BY OTHERS*</t>
-  </si>
-  <si>
-    <t>B.</t>
-  </si>
-  <si>
-    <t>ILLUMINATED STAND-UP CHANNEL LETTERS ON RAIL WITH TRIMLESS- EDGE "BEL AIRE". CUSTOM "C" CHANNEL LETTERS W/PUSH - THRU- ACRYLIC. LOADS TO EYEBROW FEATURE OVER LEASING ENTRY.- *BLOCKING AND POWER TO LOCATION BY OTHERS*</t>
-  </si>
-  <si>
-    <t>C.</t>
-  </si>
-  <si>
-    <t>ILLUMINATED GARAGE ENTRY PROJECTING SIGN / BUTTON SIGN- *BLOCKING AND POWER TO LOCATION BY OTHERS*</t>
-  </si>
-  <si>
-    <t>#2: LEASING CENTER- EXTERIOR SIGNAGE</t>
-  </si>
-  <si>
-    <t>LEASING CENTER ID - LOADS TO CANOPY ABOVE ENTRY VESTIBULE</t>
-  </si>
-  <si>
-    <t>HOURS SIGN - SUMMER / WINTER HOURS</t>
-  </si>
-  <si>
-    <t>DOUBLE DOOR VINYL KIT (LOGO, URL, PHONE) (X1 AT EACH ENTRY)</t>
-  </si>
-  <si>
-    <t>D.</t>
-  </si>
-  <si>
-    <t>"DOOR TO REMIAN UNLOCKED…" VINYL KIT (X1 AT EACH  ENTRY)</t>
-  </si>
-  <si>
-    <t>E.</t>
-  </si>
-  <si>
-    <t>ADDRESS NUMERALS - INDIVIDUAL NUMBERALS</t>
-  </si>
-  <si>
-    <t>F.</t>
-  </si>
-  <si>
-    <t>CUSTOM HANDICAP PARKING - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>G.</t>
-  </si>
-  <si>
-    <t>CUSTOM FUTURE RESIDENT PARKING - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>H.</t>
-  </si>
-  <si>
-    <t>USPS PARKING - WALL MOUNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </t>
-  </si>
-  <si>
-    <t>MANAGER ID W/ BACKER</t>
-  </si>
-  <si>
-    <t>ASSISTANT MANAGER ID W/ BACKER</t>
-  </si>
-  <si>
-    <t>EMPLOYEE ONLY (BREAKROOM)</t>
-  </si>
-  <si>
-    <t>MDF ID (EMPLOYEE BREAKROOM)</t>
-  </si>
-  <si>
-    <t>MECHANICAL ID (X1 AT EMPLOYEE BREAKROOM, X1 AT GAME,- X1 AT YOGA, X1 AT RESTROOM)</t>
-  </si>
-  <si>
-    <t>LEASING ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLUB ROOM ID </t>
-  </si>
-  <si>
-    <t>CLUB ROOM / GAME POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>I.</t>
-  </si>
-  <si>
-    <t>GAME ROOM ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </t>
-  </si>
-  <si>
-    <t>J.</t>
-  </si>
-  <si>
-    <t>VIEWING LOUNGE ID</t>
-  </si>
-  <si>
-    <t>K.</t>
-  </si>
-  <si>
-    <t>INTERNET CAFÉ ID</t>
-  </si>
-  <si>
-    <t>L.</t>
-  </si>
-  <si>
-    <t>INTERNET CAFÉ POLICY - STAND-UP</t>
-  </si>
-  <si>
-    <t>M.</t>
-  </si>
-  <si>
-    <t>WORK ROOM ID (AT INTERNET CAFÉ)</t>
-  </si>
-  <si>
-    <t>N.</t>
-  </si>
-  <si>
-    <t>MAIL ID</t>
-  </si>
-  <si>
-    <t>O.</t>
-  </si>
-  <si>
-    <t>PACKAGE ID</t>
-  </si>
-  <si>
-    <t>P.</t>
-  </si>
-  <si>
-    <t>WOMENS RSTROOM</t>
-  </si>
-  <si>
-    <t>R.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MENS RESTROOM </t>
-  </si>
-  <si>
-    <t>Q.</t>
-  </si>
-  <si>
-    <t>WORK SHARE ID</t>
-  </si>
-  <si>
-    <t>WORK SHARE POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>S.</t>
-  </si>
-  <si>
-    <t>WORK ROOM ID</t>
-  </si>
-  <si>
-    <t>T.</t>
-  </si>
-  <si>
-    <t>FITNESS ID</t>
-  </si>
-  <si>
-    <t>U.</t>
-  </si>
-  <si>
-    <t>FITNES POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>V.</t>
-  </si>
-  <si>
-    <t>YOGA STUDIO ID</t>
-  </si>
-  <si>
-    <t>W.</t>
-  </si>
-  <si>
-    <t>MAX OCCUPANCY ( LEASE, LOBBY, FITNESS, GAME, CLUBROOM, - WORK SHARE)</t>
-  </si>
-  <si>
-    <t>X.</t>
-  </si>
-  <si>
-    <t>DESKTOP PACKAGE - CUSTOM (PROP. ID, NO CASH, EQH., ETC…)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </t>
-  </si>
-  <si>
-    <t>10' CLEARANCE BAR PACKAGE (FOR CLEARANCE CHANGE)</t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING / STAIR / LEVEL</t>
-  </si>
-  <si>
-    <t>STAIRWELL ID</t>
-  </si>
-  <si>
-    <t>ELEVATOR EGRESS MAP / DO NOT USE</t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / STAIR / LEVEL (S2)</t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING (X1 AT S2, X1 AT ELEVATOR LOBBY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUILDING TO GARAGE </t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING / ELEVATOR LOBBY ID</t>
-  </si>
-  <si>
-    <t>GARAGE ACCESS</t>
-  </si>
-  <si>
-    <t>TRASH ID</t>
-  </si>
-  <si>
-    <t>TRASH / RECYCLE STAGING ID</t>
-  </si>
-  <si>
-    <t>TRASH PICK-UP / DO NOT BLOCK</t>
-  </si>
-  <si>
-    <t>EXHAUST ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </t>
-  </si>
-  <si>
-    <t>12' CLEARNCE BAR PACKAGE (AT ENTRY / CENTERED)</t>
-  </si>
-  <si>
-    <t>ENTER / EXIT / GATE WARNING SIGN PACKAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GARAGE TO BUILDING / STAIR / LEVEL </t>
-  </si>
-  <si>
-    <t>ELEVATOR  EGRESS MAP / DO NOT USE</t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING / ELEVATOR / LOBBY ID</t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING (X1 AT S6, X1 AT ELEVATOR LOBBY)</t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE (X1 EACH AT STAIR, X1 ELEVATOR LOBBY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING / ELEVATOR / LOBBY</t>
-  </si>
-  <si>
-    <t>GARAGE TO BUILDING</t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAIRWELL ID </t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE (X1 AT EACH STAIR, X1 AT ELEVATOR LOBBY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE (X1 AT ELEVATOR LOBBY)</t>
-  </si>
-  <si>
-    <t>TRASH ROOM ID</t>
-  </si>
-  <si>
-    <t>TRASH ROOM POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#10: BASEMENT SIGNAGE </t>
-  </si>
-  <si>
-    <t>UNIT DOOR NUMBERS</t>
-  </si>
-  <si>
-    <t>HALLWAY DIRECTIONALS</t>
-  </si>
-  <si>
-    <t>STAIR ACCESS EXT.</t>
-  </si>
-  <si>
-    <t>BUILDING ACCESS EXT.</t>
-  </si>
-  <si>
-    <t>STAIR / LEVEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#10: BASEMENT SIGNAGE  </t>
-  </si>
-  <si>
-    <t>RESIDENT STORAGE</t>
-  </si>
-  <si>
-    <t>ELECTRICAL ID (X1 AT BIKE AND GEAR STORAGE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL ID </t>
-  </si>
-  <si>
-    <t>DOG LOUNGE / WASH ID</t>
-  </si>
-  <si>
-    <t>DOG LOUNGE / WASH POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>BIKE AND GEAR STORAGE ID</t>
-  </si>
-  <si>
-    <t>BIKE AND GEAR STORAGE POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>ELEVATOR EGRESS MAP / DO NOT USE (E2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#11: LEVEL 1  SIGNAGE </t>
-  </si>
-  <si>
-    <t>BUILDING / ADDRESS SIGNS</t>
-  </si>
-  <si>
-    <t>HALLWAY DIRECTIONAL</t>
-  </si>
-  <si>
-    <t>UNIT ACCESS</t>
-  </si>
-  <si>
-    <t>STAIR ACCESS EXT. (S1)</t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / ELEVATOR / LOBBY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H. </t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / STAIR / LEVEL (S6)</t>
-  </si>
-  <si>
-    <t>STAIR / LEVEL ID (X1 EACH AT S7, S5, S4, S3)</t>
-  </si>
-  <si>
-    <t>STAIRWELL ID (X1 EACH AT S1, S3, S4, S5, S7)</t>
-  </si>
-  <si>
-    <t>ELECTRICAL ID</t>
-  </si>
-  <si>
-    <t>IDF ID</t>
-  </si>
-  <si>
-    <t>MAINTENANCE ID</t>
-  </si>
-  <si>
-    <t>MECHANICAL ID (AT MAINTENANCE)</t>
-  </si>
-  <si>
-    <t>FIRE DOOR / DO NOT BLOCK (X2 AT EACH)</t>
-  </si>
-  <si>
-    <t>FIRE RISER ROOM (4")</t>
-  </si>
-  <si>
-    <t>FDC WITH ADDRESS</t>
-  </si>
-  <si>
-    <t>FACP (VERIFY LOCATION)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#12: LEVEL 2 SIGNAGE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIT DOOR NUMBERS </t>
-  </si>
-  <si>
-    <t>STAIR / LEVEL ID (X1 EACH AT S1, S3, S4, S5, S7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#12: LEVEL 2 SIGNAGE  </t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / ELEVATOR LOBBY (E2)</t>
-  </si>
-  <si>
-    <t>ELEVATOR LOBBY (E3)</t>
-  </si>
-  <si>
-    <t>ELEC. / LV ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#13: LEVEL 3  SIGNAGE </t>
-  </si>
-  <si>
-    <t>LOW - VOLT ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#14: LEVEL 4  SIGNAGE </t>
-  </si>
-  <si>
-    <t>BUILDING TO GARAGE / ELEVATOR LOBBY</t>
-  </si>
-  <si>
-    <t>ROOF ACCESS (X1 AT S7, X1 AT S4)</t>
-  </si>
-  <si>
-    <t>ELEVATOR CTRL ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CITY SKY DECK ID </t>
-  </si>
-  <si>
-    <t>CITY SKY DECK POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#14: LEVEL 4  SIGNAGE  </t>
-  </si>
-  <si>
-    <t>MOUNTAIN VIEW SKY DECK ID</t>
-  </si>
-  <si>
-    <t>MOUNTAIN VIEW SKY DECK POLICY - WALL MOUNT</t>
-  </si>
-  <si>
-    <t>MAX OCCUPANCY ( X1 AT EACH SKY DECK)</t>
-  </si>
-  <si>
-    <t>UNISEX RESTROOM (X1 AT MOUNTAIN VIEW, X1 AT CITY VIEW)</t>
-  </si>
-  <si>
-    <t>FIRE DOOR / DO NOT USE (X2 AT EACH)</t>
-  </si>
-  <si>
-    <t>#15: AMENITY SIGNAGE</t>
-  </si>
-  <si>
-    <t>POOL POLICY - FENCE MOUNT</t>
-  </si>
-  <si>
-    <t>WARNING NO LIFEGUARD - FENCE MOUNT</t>
-  </si>
-  <si>
-    <t>911 PHONE - FENCE MOUNT</t>
-  </si>
-  <si>
-    <t>POOL HOURS VINYL</t>
-  </si>
-  <si>
-    <t>POOL EQUIPMENT ID</t>
-  </si>
-  <si>
-    <t>POOL CHEMICAL ID</t>
-  </si>
-  <si>
-    <t>GRILLING POLICY - STRUCTURE MOUNT (X1 AT POOL ,- X1 AT COURTYARD, X1 DOG PARK)</t>
-  </si>
-  <si>
-    <t>FIRE FEATURE GUIDELINES (X1AT POOL, X1 AT DOG PARK)</t>
-  </si>
-  <si>
-    <t>DOG PARK ID</t>
-  </si>
-  <si>
-    <t>DOG PARK POLICY - FENCE MOUNT</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -587,21 +66,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -926,72 +397,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G182"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="38.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="255.83203125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F182"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="str">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1" t="str">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="str">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="str">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="str">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>SECTION_ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>SPOTTING_KEY</v>
+      </c>
+      <c r="C2" t="str">
+        <v>SIGN_COUNT</v>
+      </c>
+      <c r="D2" t="str">
+        <v>SIGN_DESCRIPTION</v>
+      </c>
+      <c r="E2" t="str">
+        <v>EACH_COST</v>
+      </c>
+      <c r="F2" t="str">
+        <v>TOTAL_COST</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>#1: ENTRY SIGNAGE</v>
+      </c>
+      <c r="B3" t="str">
+        <v>A.</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
-        <v>16</v>
+      <c r="D3" t="str">
+        <v>ILLUMINATED DOUBLE-FACED BLADE / PROJECTING SIGNS. CUSTOM "C"- CHANNEL LETTERS W/PUSH - THRU ARCYLIC. FEATURES LED TUBE LIGHTING- ON TWO SIDES. LOADS TO ARMATURE BRACKET FURNISHED BY FOURCE.- LOADS TO BLOCKING PRIOR TO FASCIA / BRICK APPLICATION- *BLOCKING AND POWER TO LOCATION BY OTHERS*</v>
       </c>
       <c r="E3">
         <v>17880</v>
@@ -1000,18 +460,18 @@
         <v>35760</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>#1: ENTRY SIGNAGE</v>
+      </c>
+      <c r="B4" t="str">
+        <v>B.</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
+      <c r="D4" t="str">
+        <v>ILLUMINATED STAND-UP CHANNEL LETTERS ON RAIL WITH TRIMLESS- EDGE "BEL AIRE". CUSTOM "C" CHANNEL LETTERS W/PUSH - THRU- ACRYLIC. LOADS TO EYEBROW FEATURE OVER LEASING ENTRY.- *BLOCKING AND POWER TO LOCATION BY OTHERS*</v>
       </c>
       <c r="E4">
         <v>11480</v>
@@ -1020,18 +480,18 @@
         <v>11480</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>#1: ENTRY SIGNAGE</v>
+      </c>
+      <c r="B5" t="str">
+        <v>C.</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
+      <c r="D5" t="str">
+        <v>ILLUMINATED GARAGE ENTRY PROJECTING SIGN / BUTTON SIGN- *BLOCKING AND POWER TO LOCATION BY OTHERS*</v>
       </c>
       <c r="E5">
         <v>7960</v>
@@ -1040,18 +500,18 @@
         <v>7960</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
+      </c>
+      <c r="B6" t="str">
+        <v>A.</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
+      <c r="D6" t="str">
+        <v>LEASING CENTER ID - LOADS TO CANOPY ABOVE ENTRY VESTIBULE</v>
       </c>
       <c r="E6">
         <v>3800</v>
@@ -1060,18 +520,18 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
+      </c>
+      <c r="B7" t="str">
+        <v>B.</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" t="s">
-        <v>23</v>
+      <c r="D7" t="str">
+        <v>HOURS SIGN - SUMMER / WINTER HOURS</v>
       </c>
       <c r="E7">
         <v>565</v>
@@ -1080,18 +540,18 @@
         <v>565</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
+      </c>
+      <c r="B8" t="str">
+        <v>C.</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
-      <c r="D8" t="s">
-        <v>24</v>
+      <c r="D8" t="str">
+        <v>DOUBLE DOOR VINYL KIT (LOGO, URL, PHONE) (X1 AT EACH ENTRY)</v>
       </c>
       <c r="E8">
         <v>139</v>
@@ -1100,18 +560,18 @@
         <v>278</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
+      </c>
+      <c r="B9" t="str">
+        <v>D.</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
-        <v>26</v>
+      <c r="D9" t="str">
+        <v>"DOOR TO REMIAN UNLOCKED…" VINYL KIT (X1 AT EACH  ENTRY)</v>
       </c>
       <c r="E9">
         <v>69</v>
@@ -1120,18 +580,18 @@
         <v>138</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
+      </c>
+      <c r="B10" t="str">
+        <v>E.</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
-      <c r="D10" t="s">
-        <v>28</v>
+      <c r="D10" t="str">
+        <v>ADDRESS NUMERALS - INDIVIDUAL NUMBERALS</v>
       </c>
       <c r="E10">
         <v>610</v>
@@ -1140,18 +600,18 @@
         <v>610</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
+      </c>
+      <c r="B11" t="str">
+        <v>F.</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
-      <c r="D11" t="s">
-        <v>30</v>
+      <c r="D11" t="str">
+        <v>CUSTOM HANDICAP PARKING - WALL MOUNT</v>
       </c>
       <c r="E11">
         <v>415</v>
@@ -1160,18 +620,18 @@
         <v>830</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
+      </c>
+      <c r="B12" t="str">
+        <v>G.</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" t="s">
-        <v>32</v>
+      <c r="D12" t="str">
+        <v>CUSTOM FUTURE RESIDENT PARKING - WALL MOUNT</v>
       </c>
       <c r="E12">
         <v>415</v>
@@ -1180,18 +640,18 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
+      </c>
+      <c r="B13" t="str">
+        <v>H.</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
-      <c r="D13" t="s">
-        <v>34</v>
+      <c r="D13" t="str">
+        <v>USPS PARKING - WALL MOUNT</v>
       </c>
       <c r="E13">
         <v>595</v>
@@ -1200,18 +660,18 @@
         <v>595</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B14" t="str">
+        <v>A.</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
-      <c r="D14" t="s">
-        <v>36</v>
+      <c r="D14" t="str">
+        <v>MANAGER ID W/ BACKER</v>
       </c>
       <c r="E14">
         <v>78</v>
@@ -1220,18 +680,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B15" t="str">
+        <v>B.</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
-        <v>37</v>
+      <c r="D15" t="str">
+        <v>ASSISTANT MANAGER ID W/ BACKER</v>
       </c>
       <c r="E15">
         <v>78</v>
@@ -1240,18 +700,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>19</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B16" t="str">
+        <v>C.</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
-      <c r="D16" t="s">
-        <v>38</v>
+      <c r="D16" t="str">
+        <v>EMPLOYEE ONLY (BREAKROOM)</v>
       </c>
       <c r="E16">
         <v>58</v>
@@ -1260,18 +720,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>25</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B17" t="str">
+        <v>D.</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" t="s">
-        <v>39</v>
+      <c r="D17" t="str">
+        <v>MDF ID (EMPLOYEE BREAKROOM)</v>
       </c>
       <c r="E17">
         <v>58</v>
@@ -1280,18 +740,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B18" t="str">
+        <v>E.</v>
       </c>
       <c r="C18">
         <v>4</v>
       </c>
-      <c r="D18" t="s">
-        <v>40</v>
+      <c r="D18" t="str">
+        <v>MECHANICAL ID (X1 AT EMPLOYEE BREAKROOM, X1 AT GAME,- X1 AT YOGA, X1 AT RESTROOM)</v>
       </c>
       <c r="E18">
         <v>48</v>
@@ -1300,18 +760,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
-        <v>29</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B19" t="str">
+        <v>F.</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
-      <c r="D19" t="s">
-        <v>41</v>
+      <c r="D19" t="str">
+        <v>LEASING ID</v>
       </c>
       <c r="E19">
         <v>78</v>
@@ -1320,18 +780,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>31</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B20" t="str">
+        <v>G.</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
-      <c r="D20" t="s">
-        <v>42</v>
+      <c r="D20" t="str">
+        <v xml:space="preserve">CLUB ROOM ID </v>
       </c>
       <c r="E20">
         <v>78</v>
@@ -1340,18 +800,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B21" t="str">
+        <v>H.</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
-      <c r="D21" t="s">
-        <v>43</v>
+      <c r="D21" t="str">
+        <v>CLUB ROOM / GAME POLICY - WALL MOUNT</v>
       </c>
       <c r="E21">
         <v>415</v>
@@ -1360,18 +820,18 @@
         <v>415</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
+      </c>
+      <c r="B22" t="str">
+        <v>I.</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
-      <c r="D22" t="s">
-        <v>45</v>
+      <c r="D22" t="str">
+        <v>GAME ROOM ID</v>
       </c>
       <c r="E22">
         <v>68</v>
@@ -1380,18 +840,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>47</v>
+    <row r="23">
+      <c r="A23" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B23" t="str">
+        <v>J.</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
-      <c r="D23" t="s">
-        <v>48</v>
+      <c r="D23" t="str">
+        <v>VIEWING LOUNGE ID</v>
       </c>
       <c r="E23">
         <v>78</v>
@@ -1400,18 +860,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>49</v>
+    <row r="24">
+      <c r="A24" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B24" t="str">
+        <v>K.</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
-      <c r="D24" t="s">
-        <v>50</v>
+      <c r="D24" t="str">
+        <v>INTERNET CAFÉ ID</v>
       </c>
       <c r="E24">
         <v>78</v>
@@ -1420,18 +880,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
-        <v>51</v>
+    <row r="25">
+      <c r="A25" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B25" t="str">
+        <v>L.</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
-      <c r="D25" t="s">
-        <v>52</v>
+      <c r="D25" t="str">
+        <v>INTERNET CAFÉ POLICY - STAND-UP</v>
       </c>
       <c r="E25">
         <v>280</v>
@@ -1440,18 +900,18 @@
         <v>280</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
+    <row r="26">
+      <c r="A26" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B26" t="str">
+        <v>M.</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
-      <c r="D26" t="s">
-        <v>54</v>
+      <c r="D26" t="str">
+        <v>WORK ROOM ID (AT INTERNET CAFÉ)</v>
       </c>
       <c r="E26">
         <v>48</v>
@@ -1460,18 +920,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>55</v>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B27" t="str">
+        <v>N.</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
-      <c r="D27" t="s">
-        <v>56</v>
+      <c r="D27" t="str">
+        <v>MAIL ID</v>
       </c>
       <c r="E27">
         <v>78</v>
@@ -1480,18 +940,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" t="s">
-        <v>57</v>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B28" t="str">
+        <v>O.</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
-      <c r="D28" t="s">
-        <v>58</v>
+      <c r="D28" t="str">
+        <v>PACKAGE ID</v>
       </c>
       <c r="E28">
         <v>78</v>
@@ -1500,18 +960,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" t="s">
-        <v>59</v>
+    <row r="29">
+      <c r="A29" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B29" t="str">
+        <v>P.</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
-      <c r="D29" t="s">
-        <v>60</v>
+      <c r="D29" t="str">
+        <v>WOMENS RSTROOM</v>
       </c>
       <c r="E29">
         <v>98</v>
@@ -1520,18 +980,18 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
+    <row r="30">
+      <c r="A30" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B30" t="str">
+        <v>R.</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
-      <c r="D30" t="s">
-        <v>62</v>
+      <c r="D30" t="str">
+        <v xml:space="preserve">MENS RESTROOM </v>
       </c>
       <c r="E30">
         <v>98</v>
@@ -1540,18 +1000,18 @@
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" t="s">
-        <v>63</v>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B31" t="str">
+        <v>Q.</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
-      <c r="D31" t="s">
-        <v>64</v>
+      <c r="D31" t="str">
+        <v>WORK SHARE ID</v>
       </c>
       <c r="E31">
         <v>68</v>
@@ -1560,18 +1020,18 @@
         <v>136</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" t="s">
-        <v>61</v>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B32" t="str">
+        <v>R.</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
-      <c r="D32" t="s">
-        <v>65</v>
+      <c r="D32" t="str">
+        <v>WORK SHARE POLICY - WALL MOUNT</v>
       </c>
       <c r="E32">
         <v>415</v>
@@ -1580,18 +1040,18 @@
         <v>415</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B33" t="str">
+        <v>S.</v>
       </c>
       <c r="C33">
         <v>5</v>
       </c>
-      <c r="D33" t="s">
-        <v>67</v>
+      <c r="D33" t="str">
+        <v>WORK ROOM ID</v>
       </c>
       <c r="E33">
         <v>58</v>
@@ -1600,18 +1060,18 @@
         <v>290</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" t="s">
-        <v>68</v>
+    <row r="34">
+      <c r="A34" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B34" t="str">
+        <v>T.</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
-      <c r="D34" t="s">
-        <v>69</v>
+      <c r="D34" t="str">
+        <v>FITNESS ID</v>
       </c>
       <c r="E34">
         <v>78</v>
@@ -1620,18 +1080,18 @@
         <v>156</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" t="s">
-        <v>70</v>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B35" t="str">
+        <v>U.</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
-      <c r="D35" t="s">
-        <v>71</v>
+      <c r="D35" t="str">
+        <v>FITNES POLICY - WALL MOUNT</v>
       </c>
       <c r="E35">
         <v>415</v>
@@ -1640,18 +1100,18 @@
         <v>415</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" t="s">
-        <v>72</v>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B36" t="str">
+        <v>V.</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
-      <c r="D36" t="s">
-        <v>73</v>
+      <c r="D36" t="str">
+        <v>YOGA STUDIO ID</v>
       </c>
       <c r="E36">
         <v>78</v>
@@ -1660,18 +1120,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" t="s">
-        <v>74</v>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B37" t="str">
+        <v>W.</v>
       </c>
       <c r="C37">
         <v>6</v>
       </c>
-      <c r="D37" t="s">
-        <v>75</v>
+      <c r="D37" t="str">
+        <v>MAX OCCUPANCY ( LEASE, LOBBY, FITNESS, GAME, CLUBROOM, - WORK SHARE)</v>
       </c>
       <c r="E37">
         <v>58</v>
@@ -1680,18 +1140,18 @@
         <v>348</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" t="s">
-        <v>76</v>
+    <row r="38">
+      <c r="A38" t="str">
+        <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
+      </c>
+      <c r="B38" t="str">
+        <v>X.</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
-      <c r="D38" t="s">
-        <v>77</v>
+      <c r="D38" t="str">
+        <v>DESKTOP PACKAGE - CUSTOM (PROP. ID, NO CASH, EQH., ETC…)</v>
       </c>
       <c r="E38">
         <v>780</v>
@@ -1700,18 +1160,18 @@
         <v>780</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" t="s">
-        <v>15</v>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B39" t="str">
+        <v>A.</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
-      <c r="D39" t="s">
-        <v>79</v>
+      <c r="D39" t="str">
+        <v>10' CLEARANCE BAR PACKAGE (FOR CLEARANCE CHANGE)</v>
       </c>
       <c r="E39">
         <v>1095</v>
@@ -1720,18 +1180,18 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" t="s">
-        <v>17</v>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B40" t="str">
+        <v>B.</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
-      <c r="D40" t="s">
-        <v>80</v>
+      <c r="D40" t="str">
+        <v>GARAGE TO BUILDING / STAIR / LEVEL</v>
       </c>
       <c r="E40">
         <v>58</v>
@@ -1740,18 +1200,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" t="s">
-        <v>19</v>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B41" t="str">
+        <v>C.</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
-      <c r="D41" t="s">
-        <v>81</v>
+      <c r="D41" t="str">
+        <v>STAIRWELL ID</v>
       </c>
       <c r="E41">
         <v>175</v>
@@ -1760,18 +1220,18 @@
         <v>350</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>78</v>
-      </c>
-      <c r="B42" t="s">
-        <v>25</v>
+    <row r="42">
+      <c r="A42" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B42" t="str">
+        <v>D.</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
-      <c r="D42" t="s">
-        <v>82</v>
+      <c r="D42" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E42">
         <v>265</v>
@@ -1780,18 +1240,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B43" t="s">
-        <v>27</v>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B43" t="str">
+        <v>E.</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
-      <c r="D43" t="s">
-        <v>83</v>
+      <c r="D43" t="str">
+        <v>BUILDING TO GARAGE / STAIR / LEVEL (S2)</v>
       </c>
       <c r="E43">
         <v>58</v>
@@ -1800,18 +1260,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>78</v>
-      </c>
-      <c r="B44" t="s">
-        <v>29</v>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B44" t="str">
+        <v>F.</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
-      <c r="D44" t="s">
-        <v>84</v>
+      <c r="D44" t="str">
+        <v>GARAGE TO BUILDING (X1 AT S2, X1 AT ELEVATOR LOBBY)</v>
       </c>
       <c r="E44">
         <v>58</v>
@@ -1820,18 +1280,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>78</v>
-      </c>
-      <c r="B45" t="s">
-        <v>31</v>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B45" t="str">
+        <v>G.</v>
       </c>
       <c r="C45">
         <v>4</v>
       </c>
-      <c r="D45" t="s">
-        <v>85</v>
+      <c r="D45" t="str">
+        <v xml:space="preserve">BUILDING TO GARAGE </v>
       </c>
       <c r="E45">
         <v>58</v>
@@ -1840,18 +1300,18 @@
         <v>232</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>78</v>
-      </c>
-      <c r="B46" t="s">
-        <v>33</v>
+    <row r="46">
+      <c r="A46" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B46" t="str">
+        <v>H.</v>
       </c>
       <c r="C46">
         <v>2</v>
       </c>
-      <c r="D46" t="s">
-        <v>86</v>
+      <c r="D46" t="str">
+        <v>GARAGE TO BUILDING / ELEVATOR LOBBY ID</v>
       </c>
       <c r="E46">
         <v>58</v>
@@ -1860,18 +1320,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>78</v>
-      </c>
-      <c r="B47" t="s">
-        <v>44</v>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B47" t="str">
+        <v>I.</v>
       </c>
       <c r="C47">
         <v>2</v>
       </c>
-      <c r="D47" t="s">
-        <v>87</v>
+      <c r="D47" t="str">
+        <v>GARAGE ACCESS</v>
       </c>
       <c r="E47">
         <v>48</v>
@@ -1880,18 +1340,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>78</v>
-      </c>
-      <c r="B48" t="s">
-        <v>47</v>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B48" t="str">
+        <v>J.</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
-      <c r="D48" t="s">
-        <v>88</v>
+      <c r="D48" t="str">
+        <v>TRASH ID</v>
       </c>
       <c r="E48">
         <v>48</v>
@@ -1900,18 +1360,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" t="s">
-        <v>49</v>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B49" t="str">
+        <v>K.</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
-      <c r="D49" t="s">
-        <v>89</v>
+      <c r="D49" t="str">
+        <v>TRASH / RECYCLE STAGING ID</v>
       </c>
       <c r="E49">
         <v>48</v>
@@ -1920,18 +1380,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>78</v>
-      </c>
-      <c r="B50" t="s">
-        <v>51</v>
+    <row r="50">
+      <c r="A50" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B50" t="str">
+        <v>L.</v>
       </c>
       <c r="C50">
         <v>2</v>
       </c>
-      <c r="D50" t="s">
-        <v>90</v>
+      <c r="D50" t="str">
+        <v>TRASH PICK-UP / DO NOT BLOCK</v>
       </c>
       <c r="E50">
         <v>210</v>
@@ -1940,18 +1400,18 @@
         <v>420</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>78</v>
-      </c>
-      <c r="B51" t="s">
-        <v>53</v>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">#4: PARKING GARAGE BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B51" t="str">
+        <v>M.</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
-      <c r="D51" t="s">
-        <v>91</v>
+      <c r="D51" t="str">
+        <v>EXHAUST ID</v>
       </c>
       <c r="E51">
         <v>48</v>
@@ -1960,18 +1420,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>92</v>
-      </c>
-      <c r="B52" t="s">
-        <v>15</v>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B52" t="str">
+        <v>A.</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
-      <c r="D52" t="s">
-        <v>93</v>
+      <c r="D52" t="str">
+        <v>12' CLEARNCE BAR PACKAGE (AT ENTRY / CENTERED)</v>
       </c>
       <c r="E52">
         <v>1195</v>
@@ -1980,18 +1440,18 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53" t="s">
-        <v>17</v>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B53" t="str">
+        <v>B.</v>
       </c>
       <c r="C53">
         <v>2</v>
       </c>
-      <c r="D53" t="s">
-        <v>94</v>
+      <c r="D53" t="str">
+        <v>ENTER / EXIT / GATE WARNING SIGN PACKAGE</v>
       </c>
       <c r="E53">
         <v>335</v>
@@ -2000,18 +1460,18 @@
         <v>670</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>92</v>
-      </c>
-      <c r="B54" t="s">
-        <v>19</v>
+    <row r="54">
+      <c r="A54" t="str">
+        <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B54" t="str">
+        <v>C.</v>
       </c>
       <c r="C54">
         <v>2</v>
       </c>
-      <c r="D54" t="s">
-        <v>95</v>
+      <c r="D54" t="str">
+        <v xml:space="preserve">GARAGE TO BUILDING / STAIR / LEVEL </v>
       </c>
       <c r="E54">
         <v>58</v>
@@ -2020,18 +1480,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>92</v>
-      </c>
-      <c r="B55" t="s">
-        <v>25</v>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B55" t="str">
+        <v>D.</v>
       </c>
       <c r="C55">
         <v>2</v>
       </c>
-      <c r="D55" t="s">
-        <v>81</v>
+      <c r="D55" t="str">
+        <v>STAIRWELL ID</v>
       </c>
       <c r="E55">
         <v>175</v>
@@ -2040,18 +1500,18 @@
         <v>350</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>92</v>
-      </c>
-      <c r="B56" t="s">
-        <v>27</v>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B56" t="str">
+        <v>E.</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
-      <c r="D56" t="s">
-        <v>96</v>
+      <c r="D56" t="str">
+        <v>ELEVATOR  EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E56">
         <v>265</v>
@@ -2060,18 +1520,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>92</v>
-      </c>
-      <c r="B57" t="s">
-        <v>29</v>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B57" t="str">
+        <v>F.</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
-      <c r="D57" t="s">
-        <v>97</v>
+      <c r="D57" t="str">
+        <v>GARAGE TO BUILDING / ELEVATOR / LOBBY ID</v>
       </c>
       <c r="E57">
         <v>58</v>
@@ -2080,18 +1540,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>92</v>
-      </c>
-      <c r="B58" t="s">
-        <v>31</v>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B58" t="str">
+        <v>G.</v>
       </c>
       <c r="C58">
         <v>4</v>
       </c>
-      <c r="D58" t="s">
-        <v>98</v>
+      <c r="D58" t="str">
+        <v>GARAGE TO BUILDING (X1 AT S6, X1 AT ELEVATOR LOBBY)</v>
       </c>
       <c r="E58">
         <v>48</v>
@@ -2100,18 +1560,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>92</v>
-      </c>
-      <c r="B59" t="s">
-        <v>33</v>
+    <row r="59">
+      <c r="A59" t="str">
+        <v xml:space="preserve">#5: PARKING GARAGE LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B59" t="str">
+        <v>H.</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
-      <c r="D59" t="s">
-        <v>99</v>
+      <c r="D59" t="str">
+        <v>BUILDING TO GARAGE (X1 EACH AT STAIR, X1 ELEVATOR LOBBY)</v>
       </c>
       <c r="E59">
         <v>48</v>
@@ -2120,18 +1580,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>100</v>
-      </c>
-      <c r="B60" t="s">
-        <v>15</v>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B60" t="str">
+        <v>A.</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
-      <c r="D60" t="s">
-        <v>95</v>
+      <c r="D60" t="str">
+        <v xml:space="preserve">GARAGE TO BUILDING / STAIR / LEVEL </v>
       </c>
       <c r="E60">
         <v>58</v>
@@ -2140,18 +1600,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>100</v>
-      </c>
-      <c r="B61" t="s">
-        <v>17</v>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B61" t="str">
+        <v>B.</v>
       </c>
       <c r="C61">
         <v>2</v>
       </c>
-      <c r="D61" t="s">
-        <v>81</v>
+      <c r="D61" t="str">
+        <v>STAIRWELL ID</v>
       </c>
       <c r="E61">
         <v>175</v>
@@ -2160,18 +1620,18 @@
         <v>350</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>100</v>
-      </c>
-      <c r="B62" t="s">
-        <v>19</v>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B62" t="str">
+        <v>C.</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
-      <c r="D62" t="s">
-        <v>82</v>
+      <c r="D62" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E62">
         <v>265</v>
@@ -2180,18 +1640,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>100</v>
-      </c>
-      <c r="B63" t="s">
-        <v>25</v>
+    <row r="63">
+      <c r="A63" t="str">
+        <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B63" t="str">
+        <v>D.</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
-      <c r="D63" t="s">
-        <v>101</v>
+      <c r="D63" t="str">
+        <v>GARAGE TO BUILDING / ELEVATOR / LOBBY</v>
       </c>
       <c r="E63">
         <v>58</v>
@@ -2200,18 +1660,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" t="s">
-        <v>27</v>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B64" t="str">
+        <v>E.</v>
       </c>
       <c r="C64">
         <v>5</v>
       </c>
-      <c r="D64" t="s">
-        <v>102</v>
+      <c r="D64" t="str">
+        <v>GARAGE TO BUILDING</v>
       </c>
       <c r="E64">
         <v>48</v>
@@ -2220,18 +1680,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>100</v>
-      </c>
-      <c r="B65" t="s">
-        <v>29</v>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">#6: PARKING GARAGE LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B65" t="str">
+        <v>F.</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
-      <c r="D65" t="s">
-        <v>103</v>
+      <c r="D65" t="str">
+        <v>BUILDING TO GARAGE</v>
       </c>
       <c r="E65">
         <v>48</v>
@@ -2240,18 +1700,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>104</v>
-      </c>
-      <c r="B66" t="s">
-        <v>15</v>
+    <row r="66">
+      <c r="A66" t="str">
+        <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
+      </c>
+      <c r="B66" t="str">
+        <v>A.</v>
       </c>
       <c r="C66">
         <v>2</v>
       </c>
-      <c r="D66" t="s">
-        <v>95</v>
+      <c r="D66" t="str">
+        <v xml:space="preserve">GARAGE TO BUILDING / STAIR / LEVEL </v>
       </c>
       <c r="E66">
         <v>58</v>
@@ -2260,18 +1720,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>104</v>
-      </c>
-      <c r="B67" t="s">
-        <v>17</v>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
+      </c>
+      <c r="B67" t="str">
+        <v>B.</v>
       </c>
       <c r="C67">
         <v>2</v>
       </c>
-      <c r="D67" t="s">
-        <v>81</v>
+      <c r="D67" t="str">
+        <v>STAIRWELL ID</v>
       </c>
       <c r="E67">
         <v>175</v>
@@ -2280,18 +1740,18 @@
         <v>350</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>104</v>
-      </c>
-      <c r="B68" t="s">
-        <v>29</v>
+    <row r="68">
+      <c r="A68" t="str">
+        <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
+      </c>
+      <c r="B68" t="str">
+        <v>F.</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
-      <c r="D68" t="s">
-        <v>82</v>
+      <c r="D68" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E68">
         <v>265</v>
@@ -2300,18 +1760,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>104</v>
-      </c>
-      <c r="B69" t="s">
-        <v>19</v>
+    <row r="69">
+      <c r="A69" t="str">
+        <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
+      </c>
+      <c r="B69" t="str">
+        <v>C.</v>
       </c>
       <c r="C69">
         <v>1</v>
       </c>
-      <c r="D69" t="s">
-        <v>101</v>
+      <c r="D69" t="str">
+        <v>GARAGE TO BUILDING / ELEVATOR / LOBBY</v>
       </c>
       <c r="E69">
         <v>58</v>
@@ -2320,18 +1780,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>104</v>
-      </c>
-      <c r="B70" t="s">
-        <v>25</v>
+    <row r="70">
+      <c r="A70" t="str">
+        <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
+      </c>
+      <c r="B70" t="str">
+        <v>D.</v>
       </c>
       <c r="C70">
         <v>5</v>
       </c>
-      <c r="D70" t="s">
-        <v>98</v>
+      <c r="D70" t="str">
+        <v>GARAGE TO BUILDING (X1 AT S6, X1 AT ELEVATOR LOBBY)</v>
       </c>
       <c r="E70">
         <v>48</v>
@@ -2340,18 +1800,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>104</v>
-      </c>
-      <c r="B71" t="s">
-        <v>27</v>
+    <row r="71">
+      <c r="A71" t="str">
+        <v xml:space="preserve">#7: PARKING GARAGE LEVEL 3 SIGNAGE </v>
+      </c>
+      <c r="B71" t="str">
+        <v>E.</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
-      <c r="D71" t="s">
-        <v>103</v>
+      <c r="D71" t="str">
+        <v>BUILDING TO GARAGE</v>
       </c>
       <c r="E71">
         <v>48</v>
@@ -2360,18 +1820,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>105</v>
-      </c>
-      <c r="B72" t="s">
-        <v>15</v>
+    <row r="72">
+      <c r="A72" t="str">
+        <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B72" t="str">
+        <v>A.</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
-      <c r="D72" t="s">
-        <v>80</v>
+      <c r="D72" t="str">
+        <v>GARAGE TO BUILDING / STAIR / LEVEL</v>
       </c>
       <c r="E72">
         <v>58</v>
@@ -2380,18 +1840,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>105</v>
-      </c>
-      <c r="B73" t="s">
-        <v>17</v>
+    <row r="73">
+      <c r="A73" t="str">
+        <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B73" t="str">
+        <v>B.</v>
       </c>
       <c r="C73">
         <v>2</v>
       </c>
-      <c r="D73" t="s">
-        <v>106</v>
+      <c r="D73" t="str">
+        <v xml:space="preserve">STAIRWELL ID </v>
       </c>
       <c r="E73">
         <v>175</v>
@@ -2400,18 +1860,18 @@
         <v>350</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>105</v>
-      </c>
-      <c r="B74" t="s">
-        <v>19</v>
+    <row r="74">
+      <c r="A74" t="str">
+        <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B74" t="str">
+        <v>C.</v>
       </c>
       <c r="C74">
         <v>1</v>
       </c>
-      <c r="D74" t="s">
-        <v>82</v>
+      <c r="D74" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E74">
         <v>265</v>
@@ -2420,18 +1880,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>105</v>
-      </c>
-      <c r="B75" t="s">
-        <v>25</v>
+    <row r="75">
+      <c r="A75" t="str">
+        <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B75" t="str">
+        <v>D.</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
-      <c r="D75" t="s">
-        <v>101</v>
+      <c r="D75" t="str">
+        <v>GARAGE TO BUILDING / ELEVATOR / LOBBY</v>
       </c>
       <c r="E75">
         <v>58</v>
@@ -2440,18 +1900,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>105</v>
-      </c>
-      <c r="B76" t="s">
-        <v>27</v>
+    <row r="76">
+      <c r="A76" t="str">
+        <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B76" t="str">
+        <v>E.</v>
       </c>
       <c r="C76">
         <v>5</v>
       </c>
-      <c r="D76" t="s">
-        <v>98</v>
+      <c r="D76" t="str">
+        <v>GARAGE TO BUILDING (X1 AT S6, X1 AT ELEVATOR LOBBY)</v>
       </c>
       <c r="E76">
         <v>48</v>
@@ -2460,18 +1920,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>105</v>
-      </c>
-      <c r="B77" t="s">
-        <v>29</v>
+    <row r="77">
+      <c r="A77" t="str">
+        <v xml:space="preserve">#8: PARKING GARAGE LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B77" t="str">
+        <v>F.</v>
       </c>
       <c r="C77">
         <v>5</v>
       </c>
-      <c r="D77" t="s">
-        <v>107</v>
+      <c r="D77" t="str">
+        <v>BUILDING TO GARAGE (X1 AT EACH STAIR, X1 AT ELEVATOR LOBBY)</v>
       </c>
       <c r="E77">
         <v>48</v>
@@ -2480,18 +1940,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>108</v>
-      </c>
-      <c r="B78" t="s">
-        <v>15</v>
+    <row r="78">
+      <c r="A78" t="str">
+        <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
+      </c>
+      <c r="B78" t="str">
+        <v>A.</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
-      <c r="D78" t="s">
-        <v>80</v>
+      <c r="D78" t="str">
+        <v>GARAGE TO BUILDING / STAIR / LEVEL</v>
       </c>
       <c r="E78">
         <v>58</v>
@@ -2500,18 +1960,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>108</v>
-      </c>
-      <c r="B79" t="s">
-        <v>17</v>
+    <row r="79">
+      <c r="A79" t="str">
+        <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
+      </c>
+      <c r="B79" t="str">
+        <v>B.</v>
       </c>
       <c r="C79">
         <v>2</v>
       </c>
-      <c r="D79" t="s">
-        <v>81</v>
+      <c r="D79" t="str">
+        <v>STAIRWELL ID</v>
       </c>
       <c r="E79">
         <v>175</v>
@@ -2520,18 +1980,18 @@
         <v>350</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>108</v>
-      </c>
-      <c r="B80" t="s">
-        <v>19</v>
+    <row r="80">
+      <c r="A80" t="str">
+        <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
+      </c>
+      <c r="B80" t="str">
+        <v>C.</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
-      <c r="D80" t="s">
-        <v>82</v>
+      <c r="D80" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E80">
         <v>265</v>
@@ -2540,18 +2000,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>108</v>
-      </c>
-      <c r="B81" t="s">
-        <v>25</v>
+    <row r="81">
+      <c r="A81" t="str">
+        <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
+      </c>
+      <c r="B81" t="str">
+        <v>D.</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
-      <c r="D81" t="s">
-        <v>101</v>
+      <c r="D81" t="str">
+        <v>GARAGE TO BUILDING / ELEVATOR / LOBBY</v>
       </c>
       <c r="E81">
         <v>58</v>
@@ -2560,18 +2020,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>108</v>
-      </c>
-      <c r="B82" t="s">
-        <v>27</v>
+    <row r="82">
+      <c r="A82" t="str">
+        <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
+      </c>
+      <c r="B82" t="str">
+        <v>E.</v>
       </c>
       <c r="C82">
         <v>1</v>
       </c>
-      <c r="D82" t="s">
-        <v>109</v>
+      <c r="D82" t="str">
+        <v>BUILDING TO GARAGE (X1 AT ELEVATOR LOBBY)</v>
       </c>
       <c r="E82">
         <v>48</v>
@@ -2580,18 +2040,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>108</v>
-      </c>
-      <c r="B83" t="s">
-        <v>29</v>
+    <row r="83">
+      <c r="A83" t="str">
+        <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
+      </c>
+      <c r="B83" t="str">
+        <v>F.</v>
       </c>
       <c r="C83">
         <v>1</v>
       </c>
-      <c r="D83" t="s">
-        <v>110</v>
+      <c r="D83" t="str">
+        <v>TRASH ROOM ID</v>
       </c>
       <c r="E83">
         <v>58</v>
@@ -2600,18 +2060,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>108</v>
-      </c>
-      <c r="B84" t="s">
-        <v>31</v>
+    <row r="84">
+      <c r="A84" t="str">
+        <v xml:space="preserve">#9: PARKING GARAGE LEVEL 5  SIGNAGE </v>
+      </c>
+      <c r="B84" t="str">
+        <v>G.</v>
       </c>
       <c r="C84">
         <v>1</v>
       </c>
-      <c r="D84" t="s">
-        <v>111</v>
+      <c r="D84" t="str">
+        <v>TRASH ROOM POLICY - WALL MOUNT</v>
       </c>
       <c r="E84">
         <v>215</v>
@@ -2620,18 +2080,18 @@
         <v>215</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>112</v>
-      </c>
-      <c r="B85" t="s">
-        <v>15</v>
+    <row r="85">
+      <c r="A85" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B85" t="str">
+        <v>A.</v>
       </c>
       <c r="C85">
         <v>21</v>
       </c>
-      <c r="D85" t="s">
-        <v>113</v>
+      <c r="D85" t="str">
+        <v>UNIT DOOR NUMBERS</v>
       </c>
       <c r="E85">
         <v>52</v>
@@ -2640,18 +2100,18 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>112</v>
-      </c>
-      <c r="B86" t="s">
-        <v>17</v>
+    <row r="86">
+      <c r="A86" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B86" t="str">
+        <v>B.</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
-      <c r="D86" t="s">
-        <v>114</v>
+      <c r="D86" t="str">
+        <v>HALLWAY DIRECTIONALS</v>
       </c>
       <c r="E86">
         <v>125</v>
@@ -2660,18 +2120,18 @@
         <v>250</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>112</v>
-      </c>
-      <c r="B87" t="s">
-        <v>19</v>
+    <row r="87">
+      <c r="A87" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B87" t="str">
+        <v>C.</v>
       </c>
       <c r="C87">
         <v>3</v>
       </c>
-      <c r="D87" t="s">
-        <v>115</v>
+      <c r="D87" t="str">
+        <v>STAIR ACCESS EXT.</v>
       </c>
       <c r="E87">
         <v>58</v>
@@ -2680,18 +2140,18 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>112</v>
-      </c>
-      <c r="B88" t="s">
-        <v>25</v>
+    <row r="88">
+      <c r="A88" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B88" t="str">
+        <v>D.</v>
       </c>
       <c r="C88">
         <v>4</v>
       </c>
-      <c r="D88" t="s">
-        <v>116</v>
+      <c r="D88" t="str">
+        <v>BUILDING ACCESS EXT.</v>
       </c>
       <c r="E88">
         <v>58</v>
@@ -2700,18 +2160,18 @@
         <v>232</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>112</v>
-      </c>
-      <c r="B89" t="s">
-        <v>27</v>
+    <row r="89">
+      <c r="A89" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE </v>
+      </c>
+      <c r="B89" t="str">
+        <v>E.</v>
       </c>
       <c r="C89">
         <v>3</v>
       </c>
-      <c r="D89" t="s">
-        <v>117</v>
+      <c r="D89" t="str">
+        <v>STAIR / LEVEL</v>
       </c>
       <c r="E89">
         <v>58</v>
@@ -2720,18 +2180,18 @@
         <v>174</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>118</v>
-      </c>
-      <c r="B90" t="s">
-        <v>29</v>
+    <row r="90">
+      <c r="A90" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B90" t="str">
+        <v>F.</v>
       </c>
       <c r="C90">
         <v>3</v>
       </c>
-      <c r="D90" t="s">
-        <v>81</v>
+      <c r="D90" t="str">
+        <v>STAIRWELL ID</v>
       </c>
       <c r="E90">
         <v>175</v>
@@ -2740,18 +2200,18 @@
         <v>525</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>118</v>
-      </c>
-      <c r="B91" t="s">
-        <v>31</v>
+    <row r="91">
+      <c r="A91" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B91" t="str">
+        <v>G.</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
-      <c r="D91" t="s">
-        <v>83</v>
+      <c r="D91" t="str">
+        <v>BUILDING TO GARAGE / STAIR / LEVEL (S2)</v>
       </c>
       <c r="E91">
         <v>58</v>
@@ -2760,18 +2220,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>118</v>
-      </c>
-      <c r="B92" t="s">
-        <v>33</v>
+    <row r="92">
+      <c r="A92" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B92" t="str">
+        <v>H.</v>
       </c>
       <c r="C92">
         <v>3</v>
       </c>
-      <c r="D92" t="s">
-        <v>119</v>
+      <c r="D92" t="str">
+        <v>RESIDENT STORAGE</v>
       </c>
       <c r="E92">
         <v>48</v>
@@ -2780,18 +2240,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>118</v>
-      </c>
-      <c r="B93" t="s">
-        <v>44</v>
+    <row r="93">
+      <c r="A93" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B93" t="str">
+        <v>I.</v>
       </c>
       <c r="C93">
         <v>5</v>
       </c>
-      <c r="D93" t="s">
-        <v>120</v>
+      <c r="D93" t="str">
+        <v>ELECTRICAL ID (X1 AT BIKE AND GEAR STORAGE)</v>
       </c>
       <c r="E93">
         <v>48</v>
@@ -2800,18 +2260,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>118</v>
-      </c>
-      <c r="B94" t="s">
-        <v>47</v>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B94" t="str">
+        <v>J.</v>
       </c>
       <c r="C94">
         <v>1</v>
       </c>
-      <c r="D94" t="s">
-        <v>121</v>
+      <c r="D94" t="str">
+        <v xml:space="preserve">MECHANICAL ID </v>
       </c>
       <c r="E94">
         <v>48</v>
@@ -2820,18 +2280,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>118</v>
-      </c>
-      <c r="B95" t="s">
-        <v>49</v>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B95" t="str">
+        <v>K.</v>
       </c>
       <c r="C95">
         <v>1</v>
       </c>
-      <c r="D95" t="s">
-        <v>122</v>
+      <c r="D95" t="str">
+        <v>DOG LOUNGE / WASH ID</v>
       </c>
       <c r="E95">
         <v>78</v>
@@ -2840,18 +2300,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>118</v>
-      </c>
-      <c r="B96" t="s">
-        <v>51</v>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B96" t="str">
+        <v>L.</v>
       </c>
       <c r="C96">
         <v>1</v>
       </c>
-      <c r="D96" t="s">
-        <v>123</v>
+      <c r="D96" t="str">
+        <v>DOG LOUNGE / WASH POLICY - WALL MOUNT</v>
       </c>
       <c r="E96">
         <v>335</v>
@@ -2860,18 +2320,18 @@
         <v>335</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>118</v>
-      </c>
-      <c r="B97" t="s">
-        <v>53</v>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B97" t="str">
+        <v>M.</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
-      <c r="D97" t="s">
-        <v>124</v>
+      <c r="D97" t="str">
+        <v>BIKE AND GEAR STORAGE ID</v>
       </c>
       <c r="E97">
         <v>78</v>
@@ -2880,18 +2340,18 @@
         <v>156</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>118</v>
-      </c>
-      <c r="B98" t="s">
-        <v>55</v>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B98" t="str">
+        <v>N.</v>
       </c>
       <c r="C98">
         <v>1</v>
       </c>
-      <c r="D98" t="s">
-        <v>125</v>
+      <c r="D98" t="str">
+        <v>BIKE AND GEAR STORAGE POLICY - WALL MOUNT</v>
       </c>
       <c r="E98">
         <v>335</v>
@@ -2900,18 +2360,18 @@
         <v>335</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>118</v>
-      </c>
-      <c r="B99" t="s">
-        <v>57</v>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">#10: BASEMENT SIGNAGE  </v>
+      </c>
+      <c r="B99" t="str">
+        <v>O.</v>
       </c>
       <c r="C99">
         <v>1</v>
       </c>
-      <c r="D99" t="s">
-        <v>126</v>
+      <c r="D99" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE (E2)</v>
       </c>
       <c r="E99">
         <v>265</v>
@@ -2920,18 +2380,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>127</v>
-      </c>
-      <c r="B100" t="s">
-        <v>15</v>
+    <row r="100">
+      <c r="A100" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B100" t="str">
+        <v>A.</v>
       </c>
       <c r="C100">
         <v>4</v>
       </c>
-      <c r="D100" t="s">
-        <v>128</v>
+      <c r="D100" t="str">
+        <v>BUILDING / ADDRESS SIGNS</v>
       </c>
       <c r="E100">
         <v>335</v>
@@ -2940,18 +2400,18 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>127</v>
-      </c>
-      <c r="B101" t="s">
-        <v>17</v>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B101" t="str">
+        <v>B.</v>
       </c>
       <c r="C101">
         <v>75</v>
       </c>
-      <c r="D101" t="s">
-        <v>113</v>
+      <c r="D101" t="str">
+        <v>UNIT DOOR NUMBERS</v>
       </c>
       <c r="E101">
         <v>52</v>
@@ -2960,18 +2420,18 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>127</v>
-      </c>
-      <c r="B102" t="s">
-        <v>19</v>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B102" t="str">
+        <v>C.</v>
       </c>
       <c r="C102">
         <v>7</v>
       </c>
-      <c r="D102" t="s">
-        <v>129</v>
+      <c r="D102" t="str">
+        <v>HALLWAY DIRECTIONAL</v>
       </c>
       <c r="E102">
         <v>130</v>
@@ -2980,18 +2440,18 @@
         <v>910</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>127</v>
-      </c>
-      <c r="B103" t="s">
-        <v>25</v>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B103" t="str">
+        <v>D.</v>
       </c>
       <c r="C103">
         <v>1</v>
       </c>
-      <c r="D103" t="s">
-        <v>130</v>
+      <c r="D103" t="str">
+        <v>UNIT ACCESS</v>
       </c>
       <c r="E103">
         <v>48</v>
@@ -3000,18 +2460,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>127</v>
-      </c>
-      <c r="B104" t="s">
-        <v>27</v>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B104" t="str">
+        <v>E.</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
-      <c r="D104" t="s">
-        <v>131</v>
+      <c r="D104" t="str">
+        <v>STAIR ACCESS EXT. (S1)</v>
       </c>
       <c r="E104">
         <v>48</v>
@@ -3020,18 +2480,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>127</v>
-      </c>
-      <c r="B105" t="s">
-        <v>29</v>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B105" t="str">
+        <v>F.</v>
       </c>
       <c r="C105">
         <v>3</v>
       </c>
-      <c r="D105" t="s">
-        <v>116</v>
+      <c r="D105" t="str">
+        <v>BUILDING ACCESS EXT.</v>
       </c>
       <c r="E105">
         <v>48</v>
@@ -3040,18 +2500,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>127</v>
-      </c>
-      <c r="B106" t="s">
-        <v>31</v>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B106" t="str">
+        <v>G.</v>
       </c>
       <c r="C106">
         <v>1</v>
       </c>
-      <c r="D106" t="s">
-        <v>132</v>
+      <c r="D106" t="str">
+        <v>BUILDING TO GARAGE / ELEVATOR / LOBBY</v>
       </c>
       <c r="E106">
         <v>58</v>
@@ -3060,18 +2520,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>127</v>
-      </c>
-      <c r="B107" t="s">
-        <v>133</v>
+    <row r="107">
+      <c r="A107" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B107" t="str">
+        <v xml:space="preserve">H. </v>
       </c>
       <c r="C107">
         <v>1</v>
       </c>
-      <c r="D107" t="s">
-        <v>134</v>
+      <c r="D107" t="str">
+        <v>BUILDING TO GARAGE / STAIR / LEVEL (S6)</v>
       </c>
       <c r="E107">
         <v>58</v>
@@ -3080,18 +2540,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
-        <v>127</v>
-      </c>
-      <c r="B108" t="s">
-        <v>44</v>
+    <row r="108">
+      <c r="A108" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B108" t="str">
+        <v>I.</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
-      <c r="D108" t="s">
-        <v>103</v>
+      <c r="D108" t="str">
+        <v>BUILDING TO GARAGE</v>
       </c>
       <c r="E108">
         <v>48</v>
@@ -3100,18 +2560,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>127</v>
-      </c>
-      <c r="B109" t="s">
-        <v>47</v>
+    <row r="109">
+      <c r="A109" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B109" t="str">
+        <v>J.</v>
       </c>
       <c r="C109">
         <v>4</v>
       </c>
-      <c r="D109" t="s">
-        <v>135</v>
+      <c r="D109" t="str">
+        <v>STAIR / LEVEL ID (X1 EACH AT S7, S5, S4, S3)</v>
       </c>
       <c r="E109">
         <v>48</v>
@@ -3120,18 +2580,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>127</v>
-      </c>
-      <c r="B110" t="s">
-        <v>49</v>
+    <row r="110">
+      <c r="A110" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B110" t="str">
+        <v>K.</v>
       </c>
       <c r="C110">
         <v>5</v>
       </c>
-      <c r="D110" t="s">
-        <v>136</v>
+      <c r="D110" t="str">
+        <v>STAIRWELL ID (X1 EACH AT S1, S3, S4, S5, S7)</v>
       </c>
       <c r="E110">
         <v>175</v>
@@ -3140,18 +2600,18 @@
         <v>875</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>127</v>
-      </c>
-      <c r="B111" t="s">
-        <v>51</v>
+    <row r="111">
+      <c r="A111" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B111" t="str">
+        <v>L.</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
-      <c r="D111" t="s">
-        <v>82</v>
+      <c r="D111" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E111">
         <v>245</v>
@@ -3160,18 +2620,18 @@
         <v>490</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>127</v>
-      </c>
-      <c r="B112" t="s">
-        <v>53</v>
+    <row r="112">
+      <c r="A112" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B112" t="str">
+        <v>M.</v>
       </c>
       <c r="C112">
         <v>17</v>
       </c>
-      <c r="D112" t="s">
-        <v>119</v>
+      <c r="D112" t="str">
+        <v>RESIDENT STORAGE</v>
       </c>
       <c r="E112">
         <v>48</v>
@@ -3180,18 +2640,18 @@
         <v>816</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>127</v>
-      </c>
-      <c r="B113" t="s">
-        <v>55</v>
+    <row r="113">
+      <c r="A113" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B113" t="str">
+        <v>N.</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
-      <c r="D113" t="s">
-        <v>137</v>
+      <c r="D113" t="str">
+        <v>ELECTRICAL ID</v>
       </c>
       <c r="E113">
         <v>48</v>
@@ -3200,18 +2660,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>127</v>
-      </c>
-      <c r="B114" t="s">
-        <v>57</v>
+    <row r="114">
+      <c r="A114" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B114" t="str">
+        <v>O.</v>
       </c>
       <c r="C114">
         <v>4</v>
       </c>
-      <c r="D114" t="s">
-        <v>138</v>
+      <c r="D114" t="str">
+        <v>IDF ID</v>
       </c>
       <c r="E114">
         <v>48</v>
@@ -3220,18 +2680,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>127</v>
-      </c>
-      <c r="B115" t="s">
-        <v>59</v>
+    <row r="115">
+      <c r="A115" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B115" t="str">
+        <v>P.</v>
       </c>
       <c r="C115">
         <v>1</v>
       </c>
-      <c r="D115" t="s">
-        <v>139</v>
+      <c r="D115" t="str">
+        <v>MAINTENANCE ID</v>
       </c>
       <c r="E115">
         <v>48</v>
@@ -3240,18 +2700,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>127</v>
-      </c>
-      <c r="B116" t="s">
-        <v>63</v>
+    <row r="116">
+      <c r="A116" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B116" t="str">
+        <v>Q.</v>
       </c>
       <c r="C116">
         <v>1</v>
       </c>
-      <c r="D116" t="s">
-        <v>140</v>
+      <c r="D116" t="str">
+        <v>MECHANICAL ID (AT MAINTENANCE)</v>
       </c>
       <c r="E116">
         <v>48</v>
@@ -3260,18 +2720,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>127</v>
-      </c>
-      <c r="B117" t="s">
-        <v>61</v>
+    <row r="117">
+      <c r="A117" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B117" t="str">
+        <v>R.</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
-      <c r="D117" t="s">
-        <v>110</v>
+      <c r="D117" t="str">
+        <v>TRASH ROOM ID</v>
       </c>
       <c r="E117">
         <v>48</v>
@@ -3280,18 +2740,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>127</v>
-      </c>
-      <c r="B118" t="s">
-        <v>66</v>
+    <row r="118">
+      <c r="A118" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B118" t="str">
+        <v>S.</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
-      <c r="D118" t="s">
-        <v>111</v>
+      <c r="D118" t="str">
+        <v>TRASH ROOM POLICY - WALL MOUNT</v>
       </c>
       <c r="E118">
         <v>215</v>
@@ -3300,18 +2760,18 @@
         <v>215</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>127</v>
-      </c>
-      <c r="B119" t="s">
-        <v>68</v>
+    <row r="119">
+      <c r="A119" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B119" t="str">
+        <v>T.</v>
       </c>
       <c r="C119">
         <v>6</v>
       </c>
-      <c r="D119" t="s">
-        <v>141</v>
+      <c r="D119" t="str">
+        <v>FIRE DOOR / DO NOT BLOCK (X2 AT EACH)</v>
       </c>
       <c r="E119">
         <v>58</v>
@@ -3320,18 +2780,18 @@
         <v>348</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>127</v>
-      </c>
-      <c r="B120" t="s">
-        <v>70</v>
+    <row r="120">
+      <c r="A120" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B120" t="str">
+        <v>U.</v>
       </c>
       <c r="C120">
         <v>1</v>
       </c>
-      <c r="D120" t="s">
-        <v>142</v>
+      <c r="D120" t="str">
+        <v>FIRE RISER ROOM (4")</v>
       </c>
       <c r="E120">
         <v>110</v>
@@ -3340,18 +2800,18 @@
         <v>110</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>127</v>
-      </c>
-      <c r="B121" t="s">
-        <v>72</v>
+    <row r="121">
+      <c r="A121" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B121" t="str">
+        <v>V.</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
-      <c r="D121" t="s">
-        <v>143</v>
+      <c r="D121" t="str">
+        <v>FDC WITH ADDRESS</v>
       </c>
       <c r="E121">
         <v>110</v>
@@ -3360,18 +2820,18 @@
         <v>110</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>127</v>
-      </c>
-      <c r="B122" t="s">
-        <v>74</v>
+    <row r="122">
+      <c r="A122" t="str">
+        <v xml:space="preserve">#11: LEVEL 1  SIGNAGE </v>
+      </c>
+      <c r="B122" t="str">
+        <v>W.</v>
       </c>
       <c r="C122">
         <v>1</v>
       </c>
-      <c r="D122" t="s">
-        <v>144</v>
+      <c r="D122" t="str">
+        <v>FACP (VERIFY LOCATION)</v>
       </c>
       <c r="E122">
         <v>110</v>
@@ -3380,18 +2840,18 @@
         <v>110</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>145</v>
-      </c>
-      <c r="B123" t="s">
-        <v>15</v>
+    <row r="123">
+      <c r="A123" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B123" t="str">
+        <v>A.</v>
       </c>
       <c r="C123">
         <v>84</v>
       </c>
-      <c r="D123" t="s">
-        <v>146</v>
+      <c r="D123" t="str">
+        <v xml:space="preserve">UNIT DOOR NUMBERS </v>
       </c>
       <c r="E123">
         <v>48</v>
@@ -3400,18 +2860,18 @@
         <v>4032</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>145</v>
-      </c>
-      <c r="B124" t="s">
-        <v>17</v>
+    <row r="124">
+      <c r="A124" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B124" t="str">
+        <v>B.</v>
       </c>
       <c r="C124">
         <v>6</v>
       </c>
-      <c r="D124" t="s">
-        <v>129</v>
+      <c r="D124" t="str">
+        <v>HALLWAY DIRECTIONAL</v>
       </c>
       <c r="E124">
         <v>120</v>
@@ -3420,18 +2880,18 @@
         <v>720</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
-        <v>145</v>
-      </c>
-      <c r="B125" t="s">
-        <v>19</v>
+    <row r="125">
+      <c r="A125" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B125" t="str">
+        <v>C.</v>
       </c>
       <c r="C125">
         <v>5</v>
       </c>
-      <c r="D125" t="s">
-        <v>147</v>
+      <c r="D125" t="str">
+        <v>STAIR / LEVEL ID (X1 EACH AT S1, S3, S4, S5, S7)</v>
       </c>
       <c r="E125">
         <v>48</v>
@@ -3440,18 +2900,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>145</v>
-      </c>
-      <c r="B126" t="s">
-        <v>25</v>
+    <row r="126">
+      <c r="A126" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B126" t="str">
+        <v>D.</v>
       </c>
       <c r="C126">
         <v>5</v>
       </c>
-      <c r="D126" t="s">
-        <v>81</v>
+      <c r="D126" t="str">
+        <v>STAIRWELL ID</v>
       </c>
       <c r="E126">
         <v>175</v>
@@ -3460,18 +2920,18 @@
         <v>875</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
-        <v>145</v>
-      </c>
-      <c r="B127" t="s">
-        <v>27</v>
+    <row r="127">
+      <c r="A127" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE </v>
+      </c>
+      <c r="B127" t="str">
+        <v>E.</v>
       </c>
       <c r="C127">
         <v>3</v>
       </c>
-      <c r="D127" t="s">
-        <v>82</v>
+      <c r="D127" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E127">
         <v>245</v>
@@ -3480,18 +2940,18 @@
         <v>735</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
-        <v>148</v>
-      </c>
-      <c r="B128" t="s">
-        <v>29</v>
+    <row r="128">
+      <c r="A128" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B128" t="str">
+        <v>F.</v>
       </c>
       <c r="C128">
         <v>1</v>
       </c>
-      <c r="D128" t="s">
-        <v>149</v>
+      <c r="D128" t="str">
+        <v>BUILDING TO GARAGE / ELEVATOR LOBBY (E2)</v>
       </c>
       <c r="E128">
         <v>58</v>
@@ -3500,18 +2960,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>148</v>
-      </c>
-      <c r="B129" t="s">
-        <v>31</v>
+    <row r="129">
+      <c r="A129" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B129" t="str">
+        <v>G.</v>
       </c>
       <c r="C129">
         <v>1</v>
       </c>
-      <c r="D129" t="s">
-        <v>150</v>
+      <c r="D129" t="str">
+        <v>ELEVATOR LOBBY (E3)</v>
       </c>
       <c r="E129">
         <v>48</v>
@@ -3520,18 +2980,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
-        <v>148</v>
-      </c>
-      <c r="B130" t="s">
-        <v>33</v>
+    <row r="130">
+      <c r="A130" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B130" t="str">
+        <v>H.</v>
       </c>
       <c r="C130">
         <v>3</v>
       </c>
-      <c r="D130" t="s">
-        <v>103</v>
+      <c r="D130" t="str">
+        <v>BUILDING TO GARAGE</v>
       </c>
       <c r="E130">
         <v>48</v>
@@ -3540,18 +3000,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
-        <v>148</v>
-      </c>
-      <c r="B131" t="s">
-        <v>44</v>
+    <row r="131">
+      <c r="A131" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B131" t="str">
+        <v>I.</v>
       </c>
       <c r="C131">
         <v>13</v>
       </c>
-      <c r="D131" t="s">
-        <v>119</v>
+      <c r="D131" t="str">
+        <v>RESIDENT STORAGE</v>
       </c>
       <c r="E131">
         <v>48</v>
@@ -3560,18 +3020,18 @@
         <v>624</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" t="s">
-        <v>148</v>
-      </c>
-      <c r="B132" t="s">
-        <v>47</v>
+    <row r="132">
+      <c r="A132" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B132" t="str">
+        <v>J.</v>
       </c>
       <c r="C132">
         <v>5</v>
       </c>
-      <c r="D132" t="s">
-        <v>137</v>
+      <c r="D132" t="str">
+        <v>ELECTRICAL ID</v>
       </c>
       <c r="E132">
         <v>48</v>
@@ -3580,18 +3040,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" t="s">
-        <v>148</v>
-      </c>
-      <c r="B133" t="s">
-        <v>49</v>
+    <row r="133">
+      <c r="A133" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B133" t="str">
+        <v>K.</v>
       </c>
       <c r="C133">
         <v>1</v>
       </c>
-      <c r="D133" t="s">
-        <v>151</v>
+      <c r="D133" t="str">
+        <v>ELEC. / LV ID</v>
       </c>
       <c r="E133">
         <v>48</v>
@@ -3600,18 +3060,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>148</v>
-      </c>
-      <c r="B134" t="s">
-        <v>51</v>
+    <row r="134">
+      <c r="A134" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B134" t="str">
+        <v>L.</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
-      <c r="D134" t="s">
-        <v>110</v>
+      <c r="D134" t="str">
+        <v>TRASH ROOM ID</v>
       </c>
       <c r="E134">
         <v>48</v>
@@ -3620,18 +3080,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>148</v>
-      </c>
-      <c r="B135" t="s">
-        <v>53</v>
+    <row r="135">
+      <c r="A135" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B135" t="str">
+        <v>M.</v>
       </c>
       <c r="C135">
         <v>1</v>
       </c>
-      <c r="D135" t="s">
-        <v>111</v>
+      <c r="D135" t="str">
+        <v>TRASH ROOM POLICY - WALL MOUNT</v>
       </c>
       <c r="E135">
         <v>215</v>
@@ -3640,18 +3100,18 @@
         <v>215</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>148</v>
-      </c>
-      <c r="B136" t="s">
-        <v>55</v>
+    <row r="136">
+      <c r="A136" t="str">
+        <v xml:space="preserve">#12: LEVEL 2 SIGNAGE  </v>
+      </c>
+      <c r="B136" t="str">
+        <v>N.</v>
       </c>
       <c r="C136">
         <v>8</v>
       </c>
-      <c r="D136" t="s">
-        <v>141</v>
+      <c r="D136" t="str">
+        <v>FIRE DOOR / DO NOT BLOCK (X2 AT EACH)</v>
       </c>
       <c r="E136">
         <v>58</v>
@@ -3660,18 +3120,18 @@
         <v>464</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>152</v>
-      </c>
-      <c r="B137" t="s">
-        <v>15</v>
+    <row r="137">
+      <c r="A137" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B137" t="str">
+        <v>A.</v>
       </c>
       <c r="C137">
         <v>89</v>
       </c>
-      <c r="D137" t="s">
-        <v>113</v>
+      <c r="D137" t="str">
+        <v>UNIT DOOR NUMBERS</v>
       </c>
       <c r="E137">
         <v>52</v>
@@ -3680,18 +3140,18 @@
         <v>4628</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>152</v>
-      </c>
-      <c r="B138" t="s">
-        <v>17</v>
+    <row r="138">
+      <c r="A138" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B138" t="str">
+        <v>B.</v>
       </c>
       <c r="C138">
         <v>7</v>
       </c>
-      <c r="D138" t="s">
-        <v>129</v>
+      <c r="D138" t="str">
+        <v>HALLWAY DIRECTIONAL</v>
       </c>
       <c r="E138">
         <v>130</v>
@@ -3700,18 +3160,18 @@
         <v>910</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>152</v>
-      </c>
-      <c r="B139" t="s">
-        <v>19</v>
+    <row r="139">
+      <c r="A139" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B139" t="str">
+        <v>C.</v>
       </c>
       <c r="C139">
         <v>5</v>
       </c>
-      <c r="D139" t="s">
-        <v>147</v>
+      <c r="D139" t="str">
+        <v>STAIR / LEVEL ID (X1 EACH AT S1, S3, S4, S5, S7)</v>
       </c>
       <c r="E139">
         <v>58</v>
@@ -3720,18 +3180,18 @@
         <v>290</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>152</v>
-      </c>
-      <c r="B140" t="s">
-        <v>25</v>
+    <row r="140">
+      <c r="A140" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B140" t="str">
+        <v>D.</v>
       </c>
       <c r="C140">
         <v>5</v>
       </c>
-      <c r="D140" t="s">
-        <v>136</v>
+      <c r="D140" t="str">
+        <v>STAIRWELL ID (X1 EACH AT S1, S3, S4, S5, S7)</v>
       </c>
       <c r="E140">
         <v>175</v>
@@ -3740,18 +3200,18 @@
         <v>875</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>152</v>
-      </c>
-      <c r="B141" t="s">
-        <v>27</v>
+    <row r="141">
+      <c r="A141" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B141" t="str">
+        <v>E.</v>
       </c>
       <c r="C141">
         <v>2</v>
       </c>
-      <c r="D141" t="s">
-        <v>82</v>
+      <c r="D141" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E141">
         <v>265</v>
@@ -3760,18 +3220,18 @@
         <v>530</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>152</v>
-      </c>
-      <c r="B142" t="s">
-        <v>29</v>
+    <row r="142">
+      <c r="A142" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B142" t="str">
+        <v>F.</v>
       </c>
       <c r="C142">
         <v>3</v>
       </c>
-      <c r="D142" t="s">
-        <v>103</v>
+      <c r="D142" t="str">
+        <v>BUILDING TO GARAGE</v>
       </c>
       <c r="E142">
         <v>58</v>
@@ -3780,18 +3240,18 @@
         <v>174</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>152</v>
-      </c>
-      <c r="B143" t="s">
-        <v>31</v>
+    <row r="143">
+      <c r="A143" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B143" t="str">
+        <v>G.</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
-      <c r="D143" t="s">
-        <v>149</v>
+      <c r="D143" t="str">
+        <v>BUILDING TO GARAGE / ELEVATOR LOBBY (E2)</v>
       </c>
       <c r="E143">
         <v>58</v>
@@ -3800,18 +3260,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>152</v>
-      </c>
-      <c r="B144" t="s">
-        <v>33</v>
+    <row r="144">
+      <c r="A144" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B144" t="str">
+        <v>H.</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
-      <c r="D144" t="s">
-        <v>150</v>
+      <c r="D144" t="str">
+        <v>ELEVATOR LOBBY (E3)</v>
       </c>
       <c r="E144">
         <v>58</v>
@@ -3820,18 +3280,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>152</v>
-      </c>
-      <c r="B145" t="s">
-        <v>44</v>
+    <row r="145">
+      <c r="A145" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B145" t="str">
+        <v>I.</v>
       </c>
       <c r="C145">
         <v>17</v>
       </c>
-      <c r="D145" t="s">
-        <v>119</v>
+      <c r="D145" t="str">
+        <v>RESIDENT STORAGE</v>
       </c>
       <c r="E145">
         <v>48</v>
@@ -3840,18 +3300,18 @@
         <v>816</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>152</v>
-      </c>
-      <c r="B146" t="s">
-        <v>47</v>
+    <row r="146">
+      <c r="A146" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B146" t="str">
+        <v>J.</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
-      <c r="D146" t="s">
-        <v>137</v>
+      <c r="D146" t="str">
+        <v>ELECTRICAL ID</v>
       </c>
       <c r="E146">
         <v>48</v>
@@ -3860,18 +3320,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>152</v>
-      </c>
-      <c r="B147" t="s">
-        <v>49</v>
+    <row r="147">
+      <c r="A147" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B147" t="str">
+        <v>K.</v>
       </c>
       <c r="C147">
         <v>4</v>
       </c>
-      <c r="D147" t="s">
-        <v>138</v>
+      <c r="D147" t="str">
+        <v>IDF ID</v>
       </c>
       <c r="E147">
         <v>48</v>
@@ -3880,18 +3340,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>152</v>
-      </c>
-      <c r="B148" t="s">
-        <v>51</v>
+    <row r="148">
+      <c r="A148" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B148" t="str">
+        <v>L.</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
-      <c r="D148" t="s">
-        <v>153</v>
+      <c r="D148" t="str">
+        <v>LOW - VOLT ID</v>
       </c>
       <c r="E148">
         <v>48</v>
@@ -3900,18 +3360,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>152</v>
-      </c>
-      <c r="B149" t="s">
-        <v>53</v>
+    <row r="149">
+      <c r="A149" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B149" t="str">
+        <v>M.</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
-      <c r="D149" t="s">
-        <v>110</v>
+      <c r="D149" t="str">
+        <v>TRASH ROOM ID</v>
       </c>
       <c r="E149">
         <v>48</v>
@@ -3920,18 +3380,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>152</v>
-      </c>
-      <c r="B150" t="s">
-        <v>55</v>
+    <row r="150">
+      <c r="A150" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B150" t="str">
+        <v>N.</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
-      <c r="D150" t="s">
-        <v>111</v>
+      <c r="D150" t="str">
+        <v>TRASH ROOM POLICY - WALL MOUNT</v>
       </c>
       <c r="E150">
         <v>215</v>
@@ -3940,18 +3400,18 @@
         <v>215</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>152</v>
-      </c>
-      <c r="B151" t="s">
-        <v>57</v>
+    <row r="151">
+      <c r="A151" t="str">
+        <v xml:space="preserve">#13: LEVEL 3  SIGNAGE </v>
+      </c>
+      <c r="B151" t="str">
+        <v>O.</v>
       </c>
       <c r="C151">
         <v>8</v>
       </c>
-      <c r="D151" t="s">
-        <v>141</v>
+      <c r="D151" t="str">
+        <v>FIRE DOOR / DO NOT BLOCK (X2 AT EACH)</v>
       </c>
       <c r="E151">
         <v>58</v>
@@ -3960,18 +3420,18 @@
         <v>464</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
-        <v>154</v>
-      </c>
-      <c r="B152" t="s">
-        <v>15</v>
+    <row r="152">
+      <c r="A152" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B152" t="str">
+        <v>A.</v>
       </c>
       <c r="C152">
         <v>86</v>
       </c>
-      <c r="D152" t="s">
-        <v>146</v>
+      <c r="D152" t="str">
+        <v xml:space="preserve">UNIT DOOR NUMBERS </v>
       </c>
       <c r="E152">
         <v>52</v>
@@ -3980,18 +3440,18 @@
         <v>4472</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
-        <v>154</v>
-      </c>
-      <c r="B153" t="s">
-        <v>17</v>
+    <row r="153">
+      <c r="A153" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B153" t="str">
+        <v>B.</v>
       </c>
       <c r="C153">
         <v>6</v>
       </c>
-      <c r="D153" t="s">
-        <v>129</v>
+      <c r="D153" t="str">
+        <v>HALLWAY DIRECTIONAL</v>
       </c>
       <c r="E153">
         <v>130</v>
@@ -4000,18 +3460,18 @@
         <v>780</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
-        <v>154</v>
-      </c>
-      <c r="B154" t="s">
-        <v>19</v>
+    <row r="154">
+      <c r="A154" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B154" t="str">
+        <v>C.</v>
       </c>
       <c r="C154">
         <v>17</v>
       </c>
-      <c r="D154" t="s">
-        <v>119</v>
+      <c r="D154" t="str">
+        <v>RESIDENT STORAGE</v>
       </c>
       <c r="E154">
         <v>48</v>
@@ -4020,18 +3480,18 @@
         <v>816</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>154</v>
-      </c>
-      <c r="B155" t="s">
-        <v>25</v>
+    <row r="155">
+      <c r="A155" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B155" t="str">
+        <v>D.</v>
       </c>
       <c r="C155">
         <v>5</v>
       </c>
-      <c r="D155" t="s">
-        <v>147</v>
+      <c r="D155" t="str">
+        <v>STAIR / LEVEL ID (X1 EACH AT S1, S3, S4, S5, S7)</v>
       </c>
       <c r="E155">
         <v>58</v>
@@ -4040,18 +3500,18 @@
         <v>290</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>154</v>
-      </c>
-      <c r="B156" t="s">
-        <v>27</v>
+    <row r="156">
+      <c r="A156" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B156" t="str">
+        <v>E.</v>
       </c>
       <c r="C156">
         <v>5</v>
       </c>
-      <c r="D156" t="s">
-        <v>81</v>
+      <c r="D156" t="str">
+        <v>STAIRWELL ID</v>
       </c>
       <c r="E156">
         <v>175</v>
@@ -4060,18 +3520,18 @@
         <v>875</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>154</v>
-      </c>
-      <c r="B157" t="s">
-        <v>29</v>
+    <row r="157">
+      <c r="A157" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B157" t="str">
+        <v>F.</v>
       </c>
       <c r="C157">
         <v>2</v>
       </c>
-      <c r="D157" t="s">
-        <v>82</v>
+      <c r="D157" t="str">
+        <v>ELEVATOR EGRESS MAP / DO NOT USE</v>
       </c>
       <c r="E157">
         <v>265</v>
@@ -4080,18 +3540,18 @@
         <v>530</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>154</v>
-      </c>
-      <c r="B158" t="s">
-        <v>31</v>
+    <row r="158">
+      <c r="A158" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B158" t="str">
+        <v>G.</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
-      <c r="D158" t="s">
-        <v>150</v>
+      <c r="D158" t="str">
+        <v>ELEVATOR LOBBY (E3)</v>
       </c>
       <c r="E158">
         <v>58</v>
@@ -4100,18 +3560,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
-        <v>154</v>
-      </c>
-      <c r="B159" t="s">
-        <v>33</v>
+    <row r="159">
+      <c r="A159" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B159" t="str">
+        <v>H.</v>
       </c>
       <c r="C159">
         <v>3</v>
       </c>
-      <c r="D159" t="s">
-        <v>85</v>
+      <c r="D159" t="str">
+        <v xml:space="preserve">BUILDING TO GARAGE </v>
       </c>
       <c r="E159">
         <v>58</v>
@@ -4120,18 +3580,18 @@
         <v>174</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
-        <v>154</v>
-      </c>
-      <c r="B160" t="s">
-        <v>44</v>
+    <row r="160">
+      <c r="A160" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B160" t="str">
+        <v>I.</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
-      <c r="D160" t="s">
-        <v>155</v>
+      <c r="D160" t="str">
+        <v>BUILDING TO GARAGE / ELEVATOR LOBBY</v>
       </c>
       <c r="E160">
         <v>58</v>
@@ -4140,18 +3600,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>154</v>
-      </c>
-      <c r="B161" t="s">
-        <v>47</v>
+    <row r="161">
+      <c r="A161" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B161" t="str">
+        <v>J.</v>
       </c>
       <c r="C161">
         <v>6</v>
       </c>
-      <c r="D161" t="s">
-        <v>137</v>
+      <c r="D161" t="str">
+        <v>ELECTRICAL ID</v>
       </c>
       <c r="E161">
         <v>48</v>
@@ -4160,18 +3620,18 @@
         <v>288</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
-        <v>154</v>
-      </c>
-      <c r="B162" t="s">
-        <v>49</v>
+    <row r="162">
+      <c r="A162" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B162" t="str">
+        <v>K.</v>
       </c>
       <c r="C162">
         <v>2</v>
       </c>
-      <c r="D162" t="s">
-        <v>156</v>
+      <c r="D162" t="str">
+        <v>ROOF ACCESS (X1 AT S7, X1 AT S4)</v>
       </c>
       <c r="E162">
         <v>58</v>
@@ -4180,18 +3640,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
-        <v>154</v>
-      </c>
-      <c r="B163" t="s">
-        <v>51</v>
+    <row r="163">
+      <c r="A163" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B163" t="str">
+        <v>L.</v>
       </c>
       <c r="C163">
         <v>2</v>
       </c>
-      <c r="D163" t="s">
-        <v>157</v>
+      <c r="D163" t="str">
+        <v>ELEVATOR CTRL ID</v>
       </c>
       <c r="E163">
         <v>58</v>
@@ -4200,18 +3660,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A164" t="s">
-        <v>154</v>
-      </c>
-      <c r="B164" t="s">
-        <v>53</v>
+    <row r="164">
+      <c r="A164" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B164" t="str">
+        <v>M.</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
-      <c r="D164" t="s">
-        <v>158</v>
+      <c r="D164" t="str">
+        <v xml:space="preserve">CITY SKY DECK ID </v>
       </c>
       <c r="E164">
         <v>78</v>
@@ -4220,18 +3680,18 @@
         <v>78</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>154</v>
-      </c>
-      <c r="B165" t="s">
-        <v>55</v>
+    <row r="165">
+      <c r="A165" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE </v>
+      </c>
+      <c r="B165" t="str">
+        <v>N.</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
-      <c r="D165" t="s">
-        <v>159</v>
+      <c r="D165" t="str">
+        <v>CITY SKY DECK POLICY - WALL MOUNT</v>
       </c>
       <c r="E165">
         <v>415</v>
@@ -4240,18 +3700,18 @@
         <v>415</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A166" t="s">
-        <v>160</v>
-      </c>
-      <c r="B166" t="s">
-        <v>57</v>
+    <row r="166">
+      <c r="A166" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
+      </c>
+      <c r="B166" t="str">
+        <v>O.</v>
       </c>
       <c r="C166">
         <v>2</v>
       </c>
-      <c r="D166" t="s">
-        <v>161</v>
+      <c r="D166" t="str">
+        <v>MOUNTAIN VIEW SKY DECK ID</v>
       </c>
       <c r="E166">
         <v>78</v>
@@ -4260,18 +3720,18 @@
         <v>156</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A167" t="s">
-        <v>160</v>
-      </c>
-      <c r="B167" t="s">
-        <v>59</v>
+    <row r="167">
+      <c r="A167" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
+      </c>
+      <c r="B167" t="str">
+        <v>P.</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
-      <c r="D167" t="s">
-        <v>162</v>
+      <c r="D167" t="str">
+        <v>MOUNTAIN VIEW SKY DECK POLICY - WALL MOUNT</v>
       </c>
       <c r="E167">
         <v>415</v>
@@ -4280,18 +3740,18 @@
         <v>415</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A168" t="s">
-        <v>160</v>
-      </c>
-      <c r="B168" t="s">
-        <v>63</v>
+    <row r="168">
+      <c r="A168" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
+      </c>
+      <c r="B168" t="str">
+        <v>Q.</v>
       </c>
       <c r="C168">
         <v>2</v>
       </c>
-      <c r="D168" t="s">
-        <v>163</v>
+      <c r="D168" t="str">
+        <v>MAX OCCUPANCY ( X1 AT EACH SKY DECK)</v>
       </c>
       <c r="E168">
         <v>58</v>
@@ -4300,18 +3760,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A169" t="s">
-        <v>160</v>
-      </c>
-      <c r="B169" t="s">
-        <v>61</v>
+    <row r="169">
+      <c r="A169" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
+      </c>
+      <c r="B169" t="str">
+        <v>R.</v>
       </c>
       <c r="C169">
         <v>2</v>
       </c>
-      <c r="D169" t="s">
-        <v>164</v>
+      <c r="D169" t="str">
+        <v>UNISEX RESTROOM (X1 AT MOUNTAIN VIEW, X1 AT CITY VIEW)</v>
       </c>
       <c r="E169">
         <v>98</v>
@@ -4320,18 +3780,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A170" t="s">
-        <v>160</v>
-      </c>
-      <c r="B170" t="s">
-        <v>66</v>
+    <row r="170">
+      <c r="A170" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
+      </c>
+      <c r="B170" t="str">
+        <v>S.</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
-      <c r="D170" t="s">
-        <v>110</v>
+      <c r="D170" t="str">
+        <v>TRASH ROOM ID</v>
       </c>
       <c r="E170">
         <v>48</v>
@@ -4340,18 +3800,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A171" t="s">
-        <v>160</v>
-      </c>
-      <c r="B171" t="s">
-        <v>68</v>
+    <row r="171">
+      <c r="A171" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
+      </c>
+      <c r="B171" t="str">
+        <v>T.</v>
       </c>
       <c r="C171">
         <v>1</v>
       </c>
-      <c r="D171" t="s">
-        <v>111</v>
+      <c r="D171" t="str">
+        <v>TRASH ROOM POLICY - WALL MOUNT</v>
       </c>
       <c r="E171">
         <v>215</v>
@@ -4360,18 +3820,18 @@
         <v>215</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A172" t="s">
-        <v>160</v>
-      </c>
-      <c r="B172" t="s">
-        <v>70</v>
+    <row r="172">
+      <c r="A172" t="str">
+        <v xml:space="preserve">#14: LEVEL 4  SIGNAGE  </v>
+      </c>
+      <c r="B172" t="str">
+        <v>U.</v>
       </c>
       <c r="C172">
         <v>8</v>
       </c>
-      <c r="D172" t="s">
-        <v>165</v>
+      <c r="D172" t="str">
+        <v>FIRE DOOR / DO NOT USE (X2 AT EACH)</v>
       </c>
       <c r="E172">
         <v>58</v>
@@ -4380,18 +3840,18 @@
         <v>464</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A173" t="s">
-        <v>166</v>
-      </c>
-      <c r="B173" t="s">
-        <v>15</v>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B173" t="str">
+        <v>A.</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
-      <c r="D173" t="s">
-        <v>167</v>
+      <c r="D173" t="str">
+        <v>POOL POLICY - FENCE MOUNT</v>
       </c>
       <c r="E173">
         <v>715</v>
@@ -4400,18 +3860,18 @@
         <v>715</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A174" t="s">
-        <v>166</v>
-      </c>
-      <c r="B174" t="s">
-        <v>19</v>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B174" t="str">
+        <v>C.</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
-      <c r="D174" t="s">
-        <v>168</v>
+      <c r="D174" t="str">
+        <v>WARNING NO LIFEGUARD - FENCE MOUNT</v>
       </c>
       <c r="E174">
         <v>410</v>
@@ -4420,18 +3880,18 @@
         <v>410</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A175" t="s">
-        <v>166</v>
-      </c>
-      <c r="B175" t="s">
-        <v>25</v>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B175" t="str">
+        <v>D.</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
-      <c r="D175" t="s">
-        <v>169</v>
+      <c r="D175" t="str">
+        <v>911 PHONE - FENCE MOUNT</v>
       </c>
       <c r="E175">
         <v>165</v>
@@ -4440,18 +3900,18 @@
         <v>165</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A176" t="s">
-        <v>166</v>
-      </c>
-      <c r="B176" t="s">
-        <v>27</v>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B176" t="str">
+        <v>E.</v>
       </c>
       <c r="C176">
         <v>3</v>
       </c>
-      <c r="D176" t="s">
-        <v>170</v>
+      <c r="D176" t="str">
+        <v>POOL HOURS VINYL</v>
       </c>
       <c r="E176">
         <v>165</v>
@@ -4460,18 +3920,18 @@
         <v>495</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A177" t="s">
-        <v>166</v>
-      </c>
-      <c r="B177" t="s">
-        <v>29</v>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B177" t="str">
+        <v>F.</v>
       </c>
       <c r="C177">
         <v>1</v>
       </c>
-      <c r="D177" t="s">
-        <v>171</v>
+      <c r="D177" t="str">
+        <v>POOL EQUIPMENT ID</v>
       </c>
       <c r="E177">
         <v>58</v>
@@ -4480,18 +3940,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A178" t="s">
-        <v>166</v>
-      </c>
-      <c r="B178" t="s">
-        <v>31</v>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B178" t="str">
+        <v>G.</v>
       </c>
       <c r="C178">
         <v>1</v>
       </c>
-      <c r="D178" t="s">
-        <v>172</v>
+      <c r="D178" t="str">
+        <v>POOL CHEMICAL ID</v>
       </c>
       <c r="E178">
         <v>58</v>
@@ -4500,18 +3960,18 @@
         <v>58</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
-        <v>166</v>
-      </c>
-      <c r="B179" t="s">
-        <v>33</v>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B179" t="str">
+        <v>H.</v>
       </c>
       <c r="C179">
         <v>3</v>
       </c>
-      <c r="D179" t="s">
-        <v>173</v>
+      <c r="D179" t="str">
+        <v>GRILLING POLICY - STRUCTURE MOUNT (X1 AT POOL ,- X1 AT COURTYARD, X1 DOG PARK)</v>
       </c>
       <c r="E179">
         <v>335</v>
@@ -4520,18 +3980,18 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
-        <v>166</v>
-      </c>
-      <c r="B180" t="s">
-        <v>44</v>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B180" t="str">
+        <v>I.</v>
       </c>
       <c r="C180">
         <v>2</v>
       </c>
-      <c r="D180" t="s">
-        <v>174</v>
+      <c r="D180" t="str">
+        <v>FIRE FEATURE GUIDELINES (X1AT POOL, X1 AT DOG PARK)</v>
       </c>
       <c r="E180">
         <v>185</v>
@@ -4540,18 +4000,18 @@
         <v>370</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
-        <v>166</v>
-      </c>
-      <c r="B181" t="s">
-        <v>47</v>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B181" t="str">
+        <v>J.</v>
       </c>
       <c r="C181">
         <v>4</v>
       </c>
-      <c r="D181" t="s">
-        <v>175</v>
+      <c r="D181" t="str">
+        <v>DOG PARK ID</v>
       </c>
       <c r="E181">
         <v>155</v>
@@ -4560,18 +4020,18 @@
         <v>620</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>166</v>
-      </c>
-      <c r="B182" t="s">
-        <v>49</v>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>#15: AMENITY SIGNAGE</v>
+      </c>
+      <c r="B182" t="str">
+        <v>K.</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
-      <c r="D182" t="s">
-        <v>176</v>
+      <c r="D182" t="str">
+        <v>DOG PARK POLICY - FENCE MOUNT</v>
       </c>
       <c r="E182">
         <v>595</v>
@@ -4581,9 +4041,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G182 F200:G200" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F182"/>
   </ignoredErrors>
 </worksheet>
 </file>